--- a/templates/Chart_guide.xlsx
+++ b/templates/Chart_guide.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NAiri\AppData\Local\Temp\24\CitrixClient\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TPC-styleguide\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E21854F6-F326-42CC-B243-991E5D735464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891B4BBE-4063-4703-BD6F-F9946B2DDCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22290" windowHeight="12120" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="21" r:id="rId1"/>
@@ -1179,8 +1179,8 @@
     <numFmt numFmtId="169" formatCode="&quot;   &quot;@"/>
     <numFmt numFmtId="170" formatCode="&quot;* &quot;#,##0;&quot;* &quot;\-#,##0;&quot;*&quot;;&quot;* &quot;@\ "/>
     <numFmt numFmtId="171" formatCode="&quot;** &quot;#,##0;&quot;** &quot;\-#,##0;&quot;**&quot;;&quot;** &quot;@"/>
-    <numFmt numFmtId="175" formatCode=";;;"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode=";;;"/>
+    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="95">
     <font>
@@ -2425,7 +2425,7 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2549,30 +2549,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2608,9 +2585,6 @@
     </xf>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2653,18 +2627,6 @@
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="92" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="92" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="92" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="22" xfId="92" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="23" xfId="92" applyFont="1" applyBorder="1"/>
@@ -2690,50 +2652,41 @@
     <xf numFmtId="0" fontId="86" fillId="3" borderId="10" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="86" fillId="3" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="86" fillId="3" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="176" fontId="86" fillId="3" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="86" fillId="3" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="4" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="3" borderId="11" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="86" fillId="3" borderId="11" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="86" fillId="3" borderId="11" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="3" borderId="12" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="86" fillId="3" borderId="12" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="86" fillId="3" borderId="12" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="4" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="43" applyFont="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="26" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="4" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="43" applyFont="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="26" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="26" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="26" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="26" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="26" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="90" fillId="0" borderId="26" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="90" fillId="0" borderId="26" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="176" fontId="90" fillId="0" borderId="26" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="90" fillId="0" borderId="26" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="4" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="26" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="4" borderId="27" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="26" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="6" applyFont="1"/>
@@ -2745,22 +2698,10 @@
     <xf numFmtId="0" fontId="94" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -2769,32 +2710,14 @@
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2802,7 +2725,7 @@
     <xf numFmtId="165" fontId="93" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="93" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="93" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -2818,10 +2741,93 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="92" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="92" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="27" xfId="43" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="0" xfId="43" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="26" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
   </cellXfs>
   <cellStyles count="93">
     <cellStyle name="20% - Accent1 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -7872,6 +7878,524 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
+          <c:x val="1.3338274212862402E-2"/>
+          <c:y val="7.0370370370370375E-2"/>
+          <c:w val="0.97554649727641896"/>
+          <c:h val="0.87037037037037035"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="174A7C"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Line!$A$1:$Q$1</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Line!$A$2:$Q$2</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>9991081</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10622794</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10116952</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10821819</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11240815</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11425090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11533235</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11237238</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11213184</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10991496</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11145436</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11602000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11979290</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11740265</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11234147</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10429316</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10365372</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2DCC-4A5B-B57A-C07243ED4C8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="F0573E"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Line!$A$1:$Q$1</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2014</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Line!$A$3:$Q$3</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>5311411</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5402864</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5457793</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5491464</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5710759</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5890821</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2540889</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2494145</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2453741</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2507728</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2537825</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2475785</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2355803</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2312909</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2262961</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2247747</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6698800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2DCC-4A5B-B57A-C07243ED4C8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="382741983"/>
+        <c:axId val="382735263"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="382741983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:srgbClr val="000000">
+                <a:lumMod val="100000"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="850" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Avenir LT Pro 55 Roman"/>
+                <a:ea typeface="Avenir LT Pro 55 Roman"/>
+                <a:cs typeface="Avenir LT Pro 55 Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="382735263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="382735263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:extLst>
+            <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+              <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:noFill/>
+              </a14:hiddenLine>
+            </a:ext>
+          </a:extLst>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="850" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Avenir LT Pro 55 Roman"/>
+                <a:ea typeface="Avenir LT Pro 55 Roman"/>
+                <a:cs typeface="Avenir LT Pro 55 Roman"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="382741983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35812023456457975"/>
+          <c:y val="1.4814814814814815E-2"/>
+          <c:w val="0.29232193272643603"/>
+          <c:h val="6.4022163896179637E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="950" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Avenir LT Pro 55 Roman"/>
+              <a:ea typeface="Avenir LT Pro 55 Roman"/>
+              <a:cs typeface="Avenir LT Pro 55 Roman"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Avenir LT Pro 55 Roman"/>
+          <a:ea typeface="Avenir LT Pro 55 Roman"/>
+          <a:cs typeface="Avenir LT Pro 55 Roman"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
           <c:x val="7.8914141414141419E-3"/>
           <c:y val="0.1949702067998598"/>
           <c:w val="0.97327441077441079"/>
@@ -8511,7 +9035,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>('Column Distribution'!$A$9:$A$15,'Column Distribution'!$A$17:$A$21)</c:f>
+              <c:f>('Column Distribution'!$A$10:$A$16,'Column Distribution'!$A$18:$A$22)</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -8552,7 +9076,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>('Column Distribution'!$M$9:$M$15,'Column Distribution'!$M$17:$M$21)</c:f>
+              <c:f>('Column Distribution'!$M$10:$M$16,'Column Distribution'!$M$18:$M$22)</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -16297,6 +16821,46 @@
 </file>
 
 <file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -18684,6 +19248,522 @@
 </file>
 
 <file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -25651,12 +26731,12 @@
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.4501</cdr:x>
-      <cdr:y>0.87008</cdr:y>
+      <cdr:x>0.39603</cdr:x>
+      <cdr:y>0.90499</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.58315</cdr:x>
-      <cdr:y>0.91786</cdr:y>
+      <cdr:x>0.52908</cdr:x>
+      <cdr:y>0.95277</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -25671,8 +26751,8 @@
       </cdr:nvSpPr>
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4346195" y="5044124"/>
-          <a:ext cx="1284711" cy="276999"/>
+          <a:off x="3837324" y="5246517"/>
+          <a:ext cx="1289175" cy="276995"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -26662,6 +27742,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>366712</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AFF57D0-4DBB-EFC3-DF9D-4FBEB75BF47E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -27125,6 +28241,100 @@
 </file>
 
 <file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.47404</cdr:x>
+      <cdr:y>0.93493</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.64271</cdr:x>
+      <cdr:y>1</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="XAxisBox">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39CCF739-5111-046A-20ED-180B22662CBB}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2709163" y="3479800"/>
+          <a:ext cx="963917" cy="223138"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" vert="horz" wrap="none" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="850" i="1" kern="1200">
+              <a:latin typeface="Avenir LT Pro 55 Roman" panose="020B0503020203020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>X axis title (unit)</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0</cdr:x>
+      <cdr:y>0</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.55556</cdr:x>
+      <cdr:y>0.05556</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="YAxisLabelBox">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F17A491-B12A-8C09-37C1-BBC92DE063CD}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="3175000" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" vert="horz" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="en-US" sz="850" b="0" i="1" kern="1200">
+              <a:latin typeface="Avenir LT Pro 55 Roman Italic" panose="020B0503020203090204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Y axis title (unit)</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -27165,7 +28375,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -28257,13 +29467,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1356360</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>26152</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -28412,7 +29622,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="664044" cy="566928"/>
@@ -28456,15 +29666,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>667528</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76395</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1299210</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>26152</xdr:rowOff>
+      <xdr:colOff>1338088</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>35872</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -28479,8 +29689,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628650" y="3733800"/>
-          <a:ext cx="7680960" cy="721477"/>
+          <a:off x="667528" y="3789201"/>
+          <a:ext cx="7678239" cy="737028"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -28612,7 +29822,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="664044" cy="566928"/>
@@ -29496,13 +30706,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>68035</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>48207</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>440529</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>15425</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -30395,124 +31605,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="62" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="148" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="B2" s="148"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="149" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="149" t="s">
         <v>235</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
     </row>
     <row r="5" spans="1:6" ht="81" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="148" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
     </row>
     <row r="6" spans="1:6" ht="48.75" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="148" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
+      <c r="B6" s="148"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
     </row>
     <row r="7" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="148" t="s">
         <v>228</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
+      <c r="B7" s="148"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
     </row>
     <row r="8" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="148" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
     </row>
     <row r="9" spans="1:6" ht="39" customHeight="1">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="148" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
     </row>
     <row r="10" spans="1:6" ht="84.75" customHeight="1">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="148" t="s">
         <v>230</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="148"/>
     </row>
     <row r="11" spans="1:6" ht="47.25" customHeight="1">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="148" t="s">
         <v>231</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
+      <c r="B11" s="148"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="148"/>
+      <c r="F11" s="148"/>
     </row>
     <row r="12" spans="1:6" ht="47.25" customHeight="1">
-      <c r="A12" s="69" t="s">
+      <c r="A12" s="148" t="s">
         <v>232</v>
       </c>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
+      <c r="B12" s="148"/>
+      <c r="C12" s="148"/>
+      <c r="D12" s="148"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="148"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="60"/>
@@ -30523,20 +31733,15 @@
       <c r="F13" s="60"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="61"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
+      <c r="A14" s="150"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A5:F5"/>
@@ -30544,6 +31749,11 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="Download the &quot;Avenir TPC&quot; font" xr:uid="{AE17EBCF-9F1E-43C6-81CA-C7A32E44E7F0}"/>
@@ -30572,24 +31782,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="173" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
+      <c r="A2" s="173"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="14" t="s">
@@ -31060,15 +32270,15 @@
         <v>18.600000000000001</v>
       </c>
       <c r="G29" s="17"/>
-      <c r="I29" s="66" t="s">
+      <c r="I29" s="174" t="s">
         <v>78</v>
       </c>
-      <c r="J29" s="67"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="67"/>
-      <c r="M29" s="67"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="67"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="175"/>
+      <c r="M29" s="175"/>
+      <c r="N29" s="175"/>
+      <c r="O29" s="175"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="15">
@@ -31092,13 +32302,13 @@
       <c r="G30" s="18">
         <v>1980</v>
       </c>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="67"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="175"/>
+      <c r="K30" s="175"/>
+      <c r="L30" s="175"/>
+      <c r="M30" s="175"/>
+      <c r="N30" s="175"/>
+      <c r="O30" s="175"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="15">
@@ -31120,13 +32330,13 @@
         <v>19.3</v>
       </c>
       <c r="G31" s="17"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="175"/>
+      <c r="M31" s="175"/>
+      <c r="N31" s="175"/>
+      <c r="O31" s="175"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="15">
@@ -39478,814 +40688,814 @@
   <dimension ref="A1:K129"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="25.625" style="74" customWidth="1"/>
-    <col min="2" max="2" width="27.5" style="68" customWidth="1"/>
-    <col min="3" max="3" width="8" style="68" customWidth="1"/>
-    <col min="4" max="4" width="9.875" style="68" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="68" customWidth="1"/>
-    <col min="6" max="6" width="28.375" style="68" customWidth="1"/>
-    <col min="7" max="8" width="28.5" style="68" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="68"/>
+    <col min="1" max="1" width="25.625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="27.5" style="61" customWidth="1"/>
+    <col min="3" max="3" width="8" style="61" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="61" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="61" customWidth="1"/>
+    <col min="6" max="6" width="28.375" style="61" customWidth="1"/>
+    <col min="7" max="8" width="28.5" style="61" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="61"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="151" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="151" t="s">
         <v>222</v>
       </c>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="72"/>
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="63"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1">
-      <c r="A4" s="68"/>
-    </row>
-    <row r="5" spans="1:7" s="74" customFormat="1" ht="31.5">
-      <c r="A5" s="73" t="s">
+      <c r="A4" s="61"/>
+    </row>
+    <row r="5" spans="1:7" s="65" customFormat="1" ht="31.5">
+      <c r="A5" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="64" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="98" customFormat="1" ht="26.25">
-      <c r="A6" s="97" t="s">
+    <row r="6" spans="1:7" s="88" customFormat="1" ht="26.25">
+      <c r="A6" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="87" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="97">
+      <c r="C6" s="87">
         <v>18</v>
       </c>
-      <c r="D6" s="97">
+      <c r="D6" s="87">
         <v>12</v>
       </c>
-      <c r="E6" s="97" t="s">
+      <c r="E6" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="F6" s="97" t="s">
+      <c r="F6" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="G6" s="97" t="s">
+      <c r="G6" s="87" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="100" customFormat="1" ht="20.25">
-      <c r="A7" s="99" t="s">
+    <row r="7" spans="1:7" s="90" customFormat="1" ht="20.25">
+      <c r="A7" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="89" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="99">
+      <c r="C7" s="89">
         <v>16</v>
       </c>
-      <c r="D7" s="99">
+      <c r="D7" s="89">
         <v>9.5</v>
       </c>
-      <c r="E7" s="99" t="s">
+      <c r="E7" s="89" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="99" t="s">
+      <c r="F7" s="89" t="s">
         <v>131</v>
       </c>
-      <c r="G7" s="99" t="s">
+      <c r="G7" s="89" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="66">
         <v>12</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="66">
         <v>8.5</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="66" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="75" t="s">
+      <c r="G8" s="66" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="78" customFormat="1" ht="15">
-      <c r="A9" s="77" t="s">
+    <row r="9" spans="1:7" s="69" customFormat="1" ht="15">
+      <c r="A9" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="68">
         <v>11</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="68">
         <v>8.5</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="68" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="78" customFormat="1" ht="15">
-      <c r="A10" s="77" t="s">
+    <row r="10" spans="1:7" s="69" customFormat="1" ht="15">
+      <c r="A10" s="68" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="68">
         <v>11</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="68">
         <v>9.5</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="68" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="80" customFormat="1" ht="15">
-      <c r="A11" s="79" t="s">
+    <row r="11" spans="1:7" s="71" customFormat="1" ht="15">
+      <c r="A11" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="70" t="s">
         <v>239</v>
       </c>
-      <c r="C11" s="79">
+      <c r="C11" s="70">
         <v>11</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="70">
         <v>9.5</v>
       </c>
-      <c r="E11" s="79" t="s">
+      <c r="E11" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="79" t="s">
+      <c r="G11" s="70" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="78" customFormat="1" ht="15">
-      <c r="A12" s="77" t="s">
+    <row r="12" spans="1:7" s="69" customFormat="1" ht="15">
+      <c r="A12" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="68" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="68">
         <v>11</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="68">
         <v>8.5</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="68" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="77" t="s">
+      <c r="F12" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="G12" s="77" t="s">
+      <c r="G12" s="68" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="82" customFormat="1" ht="13.5">
-      <c r="A13" s="81" t="s">
+    <row r="13" spans="1:7" s="73" customFormat="1" ht="13.5">
+      <c r="A13" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="72" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="72">
         <v>10</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="72">
         <v>8</v>
       </c>
-      <c r="E13" s="81" t="s">
+      <c r="E13" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="72" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="23.25">
-      <c r="A15" s="107" t="s">
+      <c r="A15" s="151" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="107"/>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
     </row>
     <row r="17" spans="1:11" ht="31.5">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="73" t="s">
+      <c r="C17" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="73" t="s">
+      <c r="F17" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="I17" s="83" t="s">
+      <c r="I17" s="74" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="98" customFormat="1" ht="26.25">
-      <c r="A18" s="97" t="s">
+    <row r="18" spans="1:11" s="88" customFormat="1" ht="26.25">
+      <c r="A18" s="87" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="87" t="s">
         <v>239</v>
       </c>
-      <c r="C18" s="97">
+      <c r="C18" s="87">
         <v>18</v>
       </c>
-      <c r="D18" s="97">
+      <c r="D18" s="87">
         <v>12</v>
       </c>
-      <c r="E18" s="97" t="s">
+      <c r="E18" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="F18" s="97" t="s">
+      <c r="F18" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="97" t="s">
+      <c r="G18" s="87" t="s">
         <v>189</v>
       </c>
-      <c r="H18" s="97"/>
-      <c r="I18" s="97" t="s">
+      <c r="H18" s="87"/>
+      <c r="I18" s="87" t="s">
         <v>200</v>
       </c>
-      <c r="J18" s="97" t="s">
+      <c r="J18" s="87" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="100" customFormat="1" ht="20.25">
-      <c r="A19" s="99" t="s">
+    <row r="19" spans="1:11" s="90" customFormat="1" ht="20.25">
+      <c r="A19" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="89" t="s">
         <v>226</v>
       </c>
-      <c r="C19" s="99">
+      <c r="C19" s="89">
         <v>16</v>
       </c>
-      <c r="D19" s="99">
+      <c r="D19" s="89">
         <v>9.5</v>
       </c>
-      <c r="E19" s="99" t="s">
+      <c r="E19" s="89" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="99" t="s">
+      <c r="F19" s="89" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="99" t="s">
+      <c r="G19" s="89" t="s">
         <v>189</v>
       </c>
-      <c r="H19" s="99"/>
-      <c r="I19" s="99" t="s">
+      <c r="H19" s="89"/>
+      <c r="I19" s="89" t="s">
         <v>200</v>
       </c>
-      <c r="J19" s="99" t="s">
+      <c r="J19" s="89" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="80" customFormat="1" ht="15">
-      <c r="A20" s="101" t="s">
+    <row r="20" spans="1:11" s="71" customFormat="1" ht="15">
+      <c r="A20" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="101" t="s">
+      <c r="B20" s="91" t="s">
         <v>239</v>
       </c>
-      <c r="C20" s="101">
+      <c r="C20" s="91">
         <v>11</v>
       </c>
-      <c r="D20" s="101">
+      <c r="D20" s="91">
         <v>8.5</v>
       </c>
-      <c r="E20" s="101" t="s">
+      <c r="E20" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="F20" s="101" t="s">
+      <c r="F20" s="91" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="101" t="s">
+      <c r="G20" s="91" t="s">
         <v>195</v>
       </c>
-      <c r="H20" s="101" t="s">
+      <c r="H20" s="91" t="s">
         <v>192</v>
       </c>
-      <c r="I20" s="101" t="s">
+      <c r="I20" s="91" t="s">
         <v>201</v>
       </c>
-      <c r="J20" s="102"/>
-      <c r="K20" s="103"/>
-    </row>
-    <row r="21" spans="1:11" s="80" customFormat="1" ht="15">
-      <c r="A21" s="104" t="s">
+      <c r="J20" s="92"/>
+      <c r="K20" s="93"/>
+    </row>
+    <row r="21" spans="1:11" s="71" customFormat="1" ht="15">
+      <c r="A21" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="94" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="104">
+      <c r="C21" s="94">
         <v>11</v>
       </c>
-      <c r="D21" s="104">
+      <c r="D21" s="94">
         <v>8.5</v>
       </c>
-      <c r="E21" s="104" t="s">
+      <c r="E21" s="94" t="s">
         <v>134</v>
       </c>
-      <c r="F21" s="104" t="s">
+      <c r="F21" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="104" t="s">
+      <c r="G21" s="94" t="s">
         <v>195</v>
       </c>
-      <c r="H21" s="104" t="s">
+      <c r="H21" s="94" t="s">
         <v>191</v>
       </c>
-      <c r="I21" s="104" t="s">
+      <c r="I21" s="94" t="s">
         <v>201</v>
       </c>
-      <c r="J21" s="105"/>
-      <c r="K21" s="106"/>
-    </row>
-    <row r="22" spans="1:11" s="78" customFormat="1" ht="15">
-      <c r="A22" s="84" t="s">
+      <c r="J21" s="95"/>
+      <c r="K21" s="96"/>
+    </row>
+    <row r="22" spans="1:11" s="69" customFormat="1" ht="15">
+      <c r="A22" s="75" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="75" t="s">
         <v>240</v>
       </c>
-      <c r="C22" s="84">
+      <c r="C22" s="75">
         <v>11</v>
       </c>
-      <c r="D22" s="84">
+      <c r="D22" s="75">
         <v>9.5</v>
       </c>
-      <c r="E22" s="84" t="s">
+      <c r="E22" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="84" t="s">
+      <c r="F22" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="G22" s="84" t="s">
+      <c r="G22" s="75" t="s">
         <v>194</v>
       </c>
-      <c r="H22" s="84" t="s">
+      <c r="H22" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="I22" s="84" t="s">
+      <c r="I22" s="75" t="s">
         <v>202</v>
       </c>
-      <c r="J22" s="77" t="s">
+      <c r="J22" s="68" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="78" customFormat="1" ht="15">
-      <c r="A23" s="85" t="s">
+    <row r="23" spans="1:11" s="69" customFormat="1" ht="15">
+      <c r="A23" s="76" t="s">
         <v>196</v>
       </c>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="76" t="s">
         <v>240</v>
       </c>
-      <c r="C23" s="85">
+      <c r="C23" s="76">
         <v>11</v>
       </c>
-      <c r="D23" s="85">
+      <c r="D23" s="76">
         <v>9.5</v>
       </c>
-      <c r="E23" s="85" t="s">
+      <c r="E23" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="F23" s="85" t="s">
+      <c r="F23" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="G23" s="85" t="s">
+      <c r="G23" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="H23" s="85" t="s">
+      <c r="H23" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="I23" s="85" t="s">
+      <c r="I23" s="76" t="s">
         <v>202</v>
       </c>
-      <c r="J23" s="77" t="s">
+      <c r="J23" s="68" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="82" customFormat="1" ht="13.5">
-      <c r="A24" s="81" t="s">
+    <row r="24" spans="1:11" s="73" customFormat="1" ht="13.5">
+      <c r="A24" s="72" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="C24" s="81">
+      <c r="C24" s="72">
         <v>10</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="72">
         <v>8</v>
       </c>
-      <c r="E24" s="81" t="s">
+      <c r="E24" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="F24" s="81" t="s">
+      <c r="F24" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="G24" s="81" t="s">
+      <c r="G24" s="72" t="s">
         <v>189</v>
       </c>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81" t="s">
+      <c r="H24" s="72"/>
+      <c r="I24" s="72" t="s">
         <v>202</v>
       </c>
-      <c r="J24" s="81" t="s">
+      <c r="J24" s="72" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="78.75" customHeight="1">
-      <c r="A26" s="108" t="s">
+      <c r="A26" s="153" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="108"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="108"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="108"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="108"/>
+      <c r="B26" s="153"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
     </row>
     <row r="30" spans="1:11" ht="29.25">
-      <c r="A30" s="86"/>
+      <c r="A30" s="77"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="87"/>
+      <c r="A31" s="78"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="88"/>
+      <c r="A32" s="79"/>
     </row>
     <row r="33" spans="1:5" ht="72.75" customHeight="1">
-      <c r="A33" s="89"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
+      <c r="A33" s="152"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="152"/>
+      <c r="D33" s="152"/>
+      <c r="E33" s="152"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="88"/>
+      <c r="A34" s="79"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="88"/>
+      <c r="A35" s="79"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="87"/>
+      <c r="A36" s="78"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="88"/>
+      <c r="A37" s="79"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="88"/>
+      <c r="A38" s="79"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="88"/>
+      <c r="A39" s="79"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="87"/>
+      <c r="A40" s="78"/>
     </row>
     <row r="41" spans="1:5" ht="18.75">
-      <c r="A41" s="90"/>
+      <c r="A41" s="80"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="87"/>
+      <c r="A42" s="78"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="87"/>
+      <c r="A43" s="78"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="87"/>
+      <c r="A44" s="78"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="88"/>
+      <c r="A45" s="79"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="88"/>
+      <c r="A46" s="79"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="88"/>
+      <c r="A47" s="79"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="91"/>
+      <c r="A48" s="81"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="91"/>
+      <c r="A49" s="81"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="91"/>
+      <c r="A50" s="81"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="92"/>
+      <c r="A51" s="82"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="91"/>
+      <c r="A52" s="81"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="93"/>
+      <c r="A53" s="83"/>
     </row>
     <row r="54" spans="1:1" ht="18">
-      <c r="A54" s="94"/>
+      <c r="A54" s="84"/>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="92"/>
+      <c r="A55" s="82"/>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="91"/>
+      <c r="A56" s="81"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="91"/>
+      <c r="A57" s="81"/>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="93"/>
+      <c r="A58" s="83"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="91"/>
+      <c r="A59" s="81"/>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="93"/>
+      <c r="A60" s="83"/>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="91"/>
+      <c r="A61" s="81"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="93"/>
+      <c r="A62" s="83"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="91"/>
+      <c r="A63" s="81"/>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="91"/>
+      <c r="A64" s="81"/>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="92"/>
+      <c r="A65" s="82"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="93"/>
+      <c r="A66" s="83"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="93"/>
+      <c r="A67" s="83"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="91"/>
+      <c r="A68" s="81"/>
     </row>
     <row r="69" spans="1:1" ht="18">
-      <c r="A69" s="94"/>
+      <c r="A69" s="84"/>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="92"/>
+      <c r="A70" s="82"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="91"/>
+      <c r="A71" s="81"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="91"/>
+      <c r="A72" s="81"/>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="93"/>
+      <c r="A73" s="83"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="91"/>
+      <c r="A74" s="81"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="91"/>
+      <c r="A75" s="81"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="91"/>
+      <c r="A76" s="81"/>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="91"/>
+      <c r="A77" s="81"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="93"/>
+      <c r="A78" s="83"/>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="92"/>
+      <c r="A79" s="82"/>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="93"/>
+      <c r="A80" s="83"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="93"/>
+      <c r="A81" s="83"/>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="91"/>
+      <c r="A82" s="81"/>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="91"/>
+      <c r="A83" s="81"/>
     </row>
     <row r="84" spans="1:1" ht="18">
-      <c r="A84" s="94"/>
+      <c r="A84" s="84"/>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="92"/>
+      <c r="A85" s="82"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="91"/>
+      <c r="A86" s="81"/>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="91"/>
+      <c r="A87" s="81"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="93"/>
+      <c r="A88" s="83"/>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="91"/>
+      <c r="A89" s="81"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="93"/>
+      <c r="A90" s="83"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="91"/>
+      <c r="A91" s="81"/>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="93"/>
+      <c r="A92" s="83"/>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="91"/>
+      <c r="A93" s="81"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="91"/>
+      <c r="A94" s="81"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="91"/>
+      <c r="A95" s="81"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="91"/>
+      <c r="A96" s="81"/>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="93"/>
+      <c r="A97" s="83"/>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="91"/>
+      <c r="A98" s="81"/>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="91"/>
+      <c r="A99" s="81"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="91"/>
+      <c r="A100" s="81"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="92"/>
+      <c r="A101" s="82"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="93"/>
+      <c r="A102" s="83"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="93"/>
+      <c r="A103" s="83"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="91"/>
+      <c r="A104" s="81"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="91"/>
+      <c r="A105" s="81"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="91"/>
+      <c r="A106" s="81"/>
     </row>
     <row r="107" spans="1:1" ht="18">
-      <c r="A107" s="94"/>
+      <c r="A107" s="84"/>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="92"/>
+      <c r="A108" s="82"/>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="91"/>
+      <c r="A109" s="81"/>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="91"/>
+      <c r="A110" s="81"/>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="93"/>
+      <c r="A111" s="83"/>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="91"/>
+      <c r="A112" s="81"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="93"/>
+      <c r="A113" s="83"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="91"/>
+      <c r="A114" s="81"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="91"/>
+      <c r="A115" s="81"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="93"/>
+      <c r="A116" s="83"/>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="91"/>
+      <c r="A117" s="81"/>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="91"/>
+      <c r="A118" s="81"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="91"/>
+      <c r="A119" s="81"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="93"/>
+      <c r="A120" s="83"/>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="92"/>
+      <c r="A121" s="82"/>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="93"/>
+      <c r="A122" s="83"/>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="93"/>
+      <c r="A123" s="83"/>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="93"/>
+      <c r="A124" s="83"/>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="91"/>
+      <c r="A125" s="81"/>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="91"/>
+      <c r="A126" s="81"/>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="91"/>
+      <c r="A127" s="81"/>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="95"/>
+      <c r="A128" s="85"/>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="96"/>
+      <c r="A129" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -40321,45 +41531,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="6" customHeight="1"/>
-    <row r="7" spans="2:7" s="111" customFormat="1" ht="18" customHeight="1">
-      <c r="B7" s="110" t="s">
+    <row r="7" spans="2:7" s="97" customFormat="1" ht="18" customHeight="1">
+      <c r="B7" s="154" t="s">
         <v>205</v>
       </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-    </row>
-    <row r="8" spans="2:7" s="111" customFormat="1" ht="4.5" customHeight="1">
-      <c r="C8" s="112"/>
-      <c r="D8" s="113"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="115"/>
-    </row>
-    <row r="9" spans="2:7" s="111" customFormat="1">
-      <c r="B9" s="116" t="s">
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+    </row>
+    <row r="8" spans="2:7" s="97" customFormat="1" ht="4.5" customHeight="1">
+      <c r="C8" s="98"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="101"/>
+    </row>
+    <row r="9" spans="2:7" s="97" customFormat="1">
+      <c r="B9" s="102" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121"/>
-    </row>
-    <row r="10" spans="2:7" s="111" customFormat="1">
-      <c r="B10" s="116" t="s">
+      <c r="C9" s="103"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="107"/>
+    </row>
+    <row r="10" spans="2:7" s="97" customFormat="1">
+      <c r="B10" s="102" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="116"/>
+      <c r="C10" s="102"/>
     </row>
     <row r="16" spans="2:7" ht="15" customHeight="1"/>
     <row r="17" spans="13:15">
-      <c r="O17" s="122"/>
+      <c r="O17" s="108"/>
     </row>
     <row r="18" spans="13:15" ht="8.25" customHeight="1">
       <c r="M18" s="58"/>
-      <c r="O18" s="123" t="s">
+      <c r="O18" s="109" t="s">
         <v>243</v>
       </c>
     </row>
@@ -40398,19 +41608,19 @@
     </row>
     <row r="32" spans="13:15" ht="36.75" customHeight="1"/>
     <row r="33" spans="2:12" ht="45.75" customHeight="1">
-      <c r="B33" s="109" t="s">
+      <c r="B33" s="155" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="109"/>
-      <c r="J33" s="109"/>
-      <c r="K33" s="109"/>
-      <c r="L33" s="109"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="155"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="155"/>
+      <c r="L33" s="155"/>
     </row>
     <row r="34" spans="2:12" ht="3.75" customHeight="1"/>
   </sheetData>
@@ -40430,37 +41640,37 @@
   <dimension ref="L11:U17"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="9" width="9" style="124"/>
-    <col min="10" max="10" width="11.5" style="124" customWidth="1"/>
-    <col min="11" max="11" width="9" style="124" customWidth="1"/>
-    <col min="12" max="13" width="9" style="124"/>
-    <col min="14" max="14" width="2.5" style="124" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="124"/>
+    <col min="1" max="9" width="9" style="110"/>
+    <col min="10" max="10" width="11.5" style="110" customWidth="1"/>
+    <col min="11" max="11" width="9" style="110" customWidth="1"/>
+    <col min="12" max="13" width="9" style="110"/>
+    <col min="14" max="14" width="2.5" style="110" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="110"/>
   </cols>
   <sheetData>
     <row r="11" spans="12:21">
-      <c r="L11" s="124" t="s">
+      <c r="L11" s="110" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="13" spans="12:21">
-      <c r="L13" s="124" t="s">
+      <c r="L13" s="110" t="s">
         <v>208</v>
       </c>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
-      <c r="R13" s="111"/>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="111"/>
+      <c r="P13" s="97"/>
+      <c r="Q13" s="97"/>
+      <c r="R13" s="97"/>
+      <c r="S13" s="97"/>
+      <c r="T13" s="97"/>
+      <c r="U13" s="97"/>
     </row>
     <row r="15" spans="12:21">
-      <c r="L15" s="124" t="s">
+      <c r="L15" s="110" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="17" spans="12:12">
-      <c r="L17" s="124" t="s">
+      <c r="L17" s="110" t="s">
         <v>204</v>
       </c>
     </row>
@@ -40473,7 +41683,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="56"/>
@@ -40483,241 +41693,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="120" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="24.75" customHeight="1"/>
-    <row r="5" spans="1:5" ht="22.5" customHeight="1">
-      <c r="B5" s="125" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="120"/>
+    </row>
+    <row r="5" spans="1:5" ht="24.75" customHeight="1"/>
+    <row r="6" spans="1:5" ht="22.5" customHeight="1">
+      <c r="B6" s="111" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="126" t="s">
+      <c r="C6" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="126" t="s">
+      <c r="D6" s="176" t="s">
         <v>177</v>
       </c>
-      <c r="E5" s="126" t="s">
+      <c r="E6" s="112" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1">
-      <c r="B6" s="127" t="s">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1">
+      <c r="B7" s="113" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="128">
+      <c r="C7" s="114">
         <v>620814</v>
       </c>
-      <c r="D6" s="128">
+      <c r="D7" s="114">
         <v>105402</v>
       </c>
-      <c r="E6" s="129">
-        <f t="shared" ref="E6:E11" si="0">SUM(C6:D6)</f>
+      <c r="E7" s="115">
+        <f t="shared" ref="E7:E12" si="0">SUM(C7:D7)</f>
         <v>726216</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1">
-      <c r="B7" s="130" t="s">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1">
+      <c r="B8" s="116" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="131">
+      <c r="C8" s="117">
         <v>20694</v>
       </c>
-      <c r="D7" s="131">
+      <c r="D8" s="117">
         <v>391</v>
       </c>
-      <c r="E7" s="131">
+      <c r="E8" s="117">
         <f t="shared" si="0"/>
         <v>21085</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1">
-      <c r="B8" s="130" t="s">
+    <row r="9" spans="1:5" ht="18.75" customHeight="1">
+      <c r="B9" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="131">
+      <c r="C9" s="117">
         <v>4169</v>
       </c>
-      <c r="D8" s="131">
+      <c r="D9" s="117">
         <v>729</v>
       </c>
-      <c r="E8" s="131">
+      <c r="E9" s="117">
         <f t="shared" si="0"/>
         <v>4898</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18.75" customHeight="1">
-      <c r="B9" s="130" t="s">
+    <row r="10" spans="1:5" ht="18.75" customHeight="1">
+      <c r="B10" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="131">
+      <c r="C10" s="117">
         <v>98114</v>
       </c>
-      <c r="D9" s="131">
+      <c r="D10" s="117">
         <v>4706</v>
       </c>
-      <c r="E9" s="131">
+      <c r="E10" s="117">
         <f t="shared" si="0"/>
         <v>102820</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18.75" customHeight="1">
-      <c r="B10" s="130" t="s">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1">
+      <c r="B11" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="131">
+      <c r="C11" s="117">
         <v>743793</v>
       </c>
-      <c r="D10" s="131">
+      <c r="D11" s="117">
         <v>111228</v>
       </c>
-      <c r="E10" s="131">
+      <c r="E11" s="117">
         <f t="shared" si="0"/>
         <v>855021</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1">
-      <c r="B11" s="132" t="s">
+    <row r="12" spans="1:5" ht="18.75" customHeight="1">
+      <c r="B12" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="133">
+      <c r="C12" s="119">
         <v>2673985</v>
       </c>
-      <c r="D11" s="133">
+      <c r="D12" s="119">
         <v>90445</v>
       </c>
-      <c r="E11" s="133">
+      <c r="E12" s="119">
         <f t="shared" si="0"/>
         <v>2764430</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="39" customHeight="1">
-      <c r="B12" s="134" t="s">
+    <row r="13" spans="1:5" ht="39" customHeight="1">
+      <c r="B13" s="156" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13" s="59"/>
+      <c r="C13" s="157"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="157"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="59"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="136" t="s">
+      <c r="A15" s="120" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B20" s="137" t="s">
+    <row r="21" spans="2:5" ht="22.5" customHeight="1">
+      <c r="B21" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="138" t="s">
+      <c r="C21" s="122" t="s">
         <v>176</v>
       </c>
-      <c r="D20" s="138" t="s">
+      <c r="D21" s="177" t="s">
         <v>177</v>
       </c>
-      <c r="E20" s="138" t="s">
+      <c r="E21" s="122" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B21" s="139" t="s">
+    <row r="22" spans="2:5" ht="18.75" customHeight="1">
+      <c r="B22" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="140">
+      <c r="C22" s="124">
         <v>620814</v>
       </c>
-      <c r="D21" s="140">
+      <c r="D22" s="124">
         <v>105402</v>
       </c>
-      <c r="E21" s="141">
+      <c r="E22" s="125">
         <v>726216</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B22" s="142" t="s">
+    <row r="23" spans="2:5" ht="18.75" customHeight="1">
+      <c r="B23" s="126" t="s">
         <v>247</v>
       </c>
-      <c r="C22" s="140">
+      <c r="C23" s="124">
         <v>20694</v>
       </c>
-      <c r="D22" s="140">
+      <c r="D23" s="124">
         <v>391</v>
       </c>
-      <c r="E22" s="140">
+      <c r="E23" s="124">
         <v>21085</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B23" s="139" t="s">
+    <row r="24" spans="2:5" ht="18.75" customHeight="1">
+      <c r="B24" s="123" t="s">
         <v>180</v>
       </c>
-      <c r="C23" s="140">
+      <c r="C24" s="124">
         <v>4169</v>
       </c>
-      <c r="D23" s="140">
+      <c r="D24" s="124">
         <v>729</v>
       </c>
-      <c r="E23" s="140">
+      <c r="E24" s="124">
         <v>4898</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B24" s="142" t="s">
+    <row r="25" spans="2:5" ht="18.75" customHeight="1">
+      <c r="B25" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="C24" s="140">
+      <c r="C25" s="124">
         <v>98114</v>
       </c>
-      <c r="D24" s="140">
+      <c r="D25" s="124">
         <v>4706</v>
       </c>
-      <c r="E24" s="140">
+      <c r="E25" s="124">
         <v>102820</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B25" s="139" t="s">
+    <row r="26" spans="2:5" ht="18.75" customHeight="1">
+      <c r="B26" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="140">
+      <c r="C26" s="124">
         <v>743793</v>
       </c>
-      <c r="D25" s="140">
+      <c r="D26" s="124">
         <v>111228</v>
       </c>
-      <c r="E25" s="140">
+      <c r="E26" s="124">
         <v>855021</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B26" s="139" t="s">
+    <row r="27" spans="2:5" ht="18.75" customHeight="1">
+      <c r="B27" s="123" t="s">
         <v>183</v>
       </c>
-      <c r="C26" s="140">
+      <c r="C27" s="124">
         <v>2673985</v>
       </c>
-      <c r="D26" s="140">
+      <c r="D27" s="124">
         <v>90445</v>
       </c>
-      <c r="E26" s="140">
+      <c r="E27" s="124">
         <v>2764430</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="41.25" customHeight="1">
-      <c r="B27" s="143" t="s">
+    <row r="28" spans="2:5" ht="41.25" customHeight="1">
+      <c r="B28" s="158" t="s">
         <v>249</v>
       </c>
-      <c r="C27" s="143"/>
-      <c r="D27" s="143"/>
-      <c r="E27" s="143"/>
+      <c r="C28" s="158"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -41049,10 +42262,10 @@
         <f t="shared" si="2"/>
         <v>0.222</v>
       </c>
-      <c r="F38" s="144"/>
-      <c r="G38" s="144"/>
-      <c r="H38" s="144"/>
-      <c r="I38" s="144"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="127"/>
     </row>
     <row r="39" spans="2:9">
       <c r="B39" s="36" t="s">
@@ -41094,1426 +42307,1426 @@
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO24"/>
+  <dimension ref="A2:AO25"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="13.625" style="146" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="146" customWidth="1"/>
-    <col min="3" max="3" width="1.5" style="146" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="146" customWidth="1"/>
-    <col min="5" max="5" width="2.875" style="146" customWidth="1"/>
-    <col min="6" max="6" width="1.5" style="146" customWidth="1"/>
-    <col min="7" max="7" width="9.5" style="146" customWidth="1"/>
-    <col min="8" max="8" width="2.875" style="146" customWidth="1"/>
-    <col min="9" max="9" width="1.5" style="146" customWidth="1"/>
-    <col min="10" max="10" width="9.375" style="146" customWidth="1"/>
-    <col min="11" max="11" width="2.875" style="146" customWidth="1"/>
-    <col min="12" max="12" width="1.5" style="146" customWidth="1"/>
-    <col min="13" max="13" width="7.5" style="146" customWidth="1"/>
-    <col min="14" max="14" width="2.875" style="146" customWidth="1"/>
-    <col min="15" max="15" width="1.5" style="146" customWidth="1"/>
-    <col min="16" max="16" width="8.5" style="146" customWidth="1"/>
-    <col min="17" max="17" width="2.875" style="146" customWidth="1"/>
-    <col min="18" max="18" width="1.5" style="146" customWidth="1"/>
-    <col min="19" max="19" width="8.5" style="146" customWidth="1"/>
-    <col min="20" max="22" width="7" style="146"/>
-    <col min="23" max="24" width="3.625" style="146" customWidth="1"/>
-    <col min="25" max="25" width="7.125" style="146" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7" style="146"/>
-    <col min="27" max="27" width="3.625" style="146" customWidth="1"/>
-    <col min="28" max="28" width="7.125" style="146" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7" style="146"/>
-    <col min="30" max="30" width="3.625" style="146" customWidth="1"/>
-    <col min="31" max="31" width="7.875" style="146" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7" style="146"/>
-    <col min="33" max="33" width="3.625" style="146" customWidth="1"/>
-    <col min="34" max="34" width="7.125" style="146" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7" style="146"/>
-    <col min="36" max="36" width="3.625" style="146" customWidth="1"/>
-    <col min="37" max="37" width="7.125" style="146" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7" style="146"/>
-    <col min="39" max="39" width="3.625" style="146" customWidth="1"/>
-    <col min="40" max="40" width="9.5" style="146" customWidth="1"/>
-    <col min="41" max="16384" width="7" style="146"/>
+    <col min="1" max="1" width="13.625" style="129" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="129" customWidth="1"/>
+    <col min="3" max="3" width="1.5" style="129" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="129" customWidth="1"/>
+    <col min="5" max="5" width="2.875" style="129" customWidth="1"/>
+    <col min="6" max="6" width="1.5" style="129" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="129" customWidth="1"/>
+    <col min="8" max="8" width="2.875" style="129" customWidth="1"/>
+    <col min="9" max="9" width="1.5" style="129" customWidth="1"/>
+    <col min="10" max="10" width="9.375" style="129" customWidth="1"/>
+    <col min="11" max="11" width="2.875" style="129" customWidth="1"/>
+    <col min="12" max="12" width="1.5" style="129" customWidth="1"/>
+    <col min="13" max="13" width="7.5" style="129" customWidth="1"/>
+    <col min="14" max="14" width="2.875" style="129" customWidth="1"/>
+    <col min="15" max="15" width="1.5" style="129" customWidth="1"/>
+    <col min="16" max="16" width="8.5" style="129" customWidth="1"/>
+    <col min="17" max="17" width="2.875" style="129" customWidth="1"/>
+    <col min="18" max="18" width="1.5" style="129" customWidth="1"/>
+    <col min="19" max="19" width="8.5" style="129" customWidth="1"/>
+    <col min="20" max="22" width="7" style="129"/>
+    <col min="23" max="24" width="3.625" style="129" customWidth="1"/>
+    <col min="25" max="25" width="7.125" style="129" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7" style="129"/>
+    <col min="27" max="27" width="3.625" style="129" customWidth="1"/>
+    <col min="28" max="28" width="7.125" style="129" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7" style="129"/>
+    <col min="30" max="30" width="3.625" style="129" customWidth="1"/>
+    <col min="31" max="31" width="7.875" style="129" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7" style="129"/>
+    <col min="33" max="33" width="3.625" style="129" customWidth="1"/>
+    <col min="34" max="34" width="7.125" style="129" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7" style="129"/>
+    <col min="36" max="36" width="3.625" style="129" customWidth="1"/>
+    <col min="37" max="37" width="7.125" style="129" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7" style="129"/>
+    <col min="39" max="39" width="3.625" style="129" customWidth="1"/>
+    <col min="40" max="40" width="9.5" style="129" customWidth="1"/>
+    <col min="41" max="16384" width="7" style="129"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="15.75">
-      <c r="A1" s="145" t="s">
+    <row r="2" spans="1:41" ht="15.75">
+      <c r="A2" s="168" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="V1" s="145" t="s">
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="168"/>
+      <c r="S2" s="168"/>
+      <c r="V2" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="145"/>
-      <c r="Z1" s="145"/>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="145"/>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="145"/>
-      <c r="AG1" s="145"/>
-      <c r="AH1" s="145"/>
-      <c r="AI1" s="145"/>
-      <c r="AJ1" s="145"/>
-      <c r="AK1" s="145"/>
-      <c r="AL1" s="145"/>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="145"/>
-      <c r="AO1" s="174"/>
-    </row>
-    <row r="2" spans="1:41" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="W2" s="168"/>
+      <c r="X2" s="168"/>
+      <c r="Y2" s="168"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="168"/>
+      <c r="AB2" s="168"/>
+      <c r="AC2" s="168"/>
+      <c r="AD2" s="168"/>
+      <c r="AE2" s="168"/>
+      <c r="AF2" s="168"/>
+      <c r="AG2" s="168"/>
+      <c r="AH2" s="168"/>
+      <c r="AI2" s="168"/>
+      <c r="AJ2" s="168"/>
+      <c r="AK2" s="168"/>
+      <c r="AL2" s="168"/>
+      <c r="AM2" s="168"/>
+      <c r="AN2" s="168"/>
+      <c r="AO2" s="128"/>
+    </row>
+    <row r="3" spans="1:41" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A3" s="168" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="145"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="145"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="147"/>
-      <c r="Y2" s="147"/>
-      <c r="Z2" s="147"/>
-      <c r="AA2" s="147"/>
-      <c r="AB2" s="147"/>
-      <c r="AC2" s="147"/>
-      <c r="AD2" s="147"/>
-      <c r="AE2" s="147"/>
-      <c r="AF2" s="147"/>
-      <c r="AG2" s="147"/>
-      <c r="AH2" s="147"/>
-      <c r="AI2" s="147"/>
-      <c r="AJ2" s="147"/>
-      <c r="AK2" s="147"/>
-      <c r="AL2" s="147"/>
-      <c r="AM2" s="147"/>
-      <c r="AN2" s="147"/>
-      <c r="AO2" s="147"/>
-    </row>
-    <row r="3" spans="1:41" ht="15" thickTop="1" thickBot="1">
-      <c r="A3" s="147"/>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="147"/>
-      <c r="O3" s="147"/>
-      <c r="P3" s="147"/>
-      <c r="Q3" s="147"/>
-      <c r="R3" s="147"/>
-      <c r="S3" s="147"/>
-      <c r="U3" s="148"/>
-      <c r="V3" s="148" t="s">
+      <c r="B3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
+      <c r="L3" s="168"/>
+      <c r="M3" s="168"/>
+      <c r="N3" s="168"/>
+      <c r="O3" s="168"/>
+      <c r="P3" s="168"/>
+      <c r="Q3" s="168"/>
+      <c r="R3" s="168"/>
+      <c r="S3" s="168"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="130"/>
+      <c r="W3" s="130"/>
+      <c r="X3" s="130"/>
+      <c r="Y3" s="130"/>
+      <c r="Z3" s="130"/>
+      <c r="AA3" s="130"/>
+      <c r="AB3" s="130"/>
+      <c r="AC3" s="130"/>
+      <c r="AD3" s="130"/>
+      <c r="AE3" s="130"/>
+      <c r="AF3" s="130"/>
+      <c r="AG3" s="130"/>
+      <c r="AH3" s="130"/>
+      <c r="AI3" s="130"/>
+      <c r="AJ3" s="130"/>
+      <c r="AK3" s="130"/>
+      <c r="AL3" s="130"/>
+      <c r="AM3" s="130"/>
+      <c r="AN3" s="130"/>
+      <c r="AO3" s="130"/>
+    </row>
+    <row r="4" spans="1:41" ht="15" thickTop="1" thickBot="1">
+      <c r="A4" s="130"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="130"/>
+      <c r="U4" s="164"/>
+      <c r="V4" s="164" t="s">
         <v>210</v>
       </c>
-      <c r="W3" s="148"/>
-      <c r="X3" s="149"/>
-      <c r="Y3" s="148" t="s">
+      <c r="W4" s="164"/>
+      <c r="X4" s="131"/>
+      <c r="Y4" s="164" t="s">
         <v>211</v>
       </c>
-      <c r="Z3" s="148"/>
-      <c r="AA3" s="150"/>
-      <c r="AB3" s="148" t="s">
+      <c r="Z4" s="164"/>
+      <c r="AA4" s="132"/>
+      <c r="AB4" s="164" t="s">
         <v>212</v>
       </c>
-      <c r="AC3" s="148"/>
-      <c r="AD3" s="149"/>
-      <c r="AE3" s="148" t="s">
+      <c r="AC4" s="164"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="164" t="s">
         <v>46</v>
       </c>
-      <c r="AF3" s="151"/>
-      <c r="AG3" s="151"/>
-      <c r="AH3" s="151"/>
-      <c r="AI3" s="151"/>
-      <c r="AJ3" s="152"/>
-      <c r="AK3" s="148" t="s">
+      <c r="AF4" s="169"/>
+      <c r="AG4" s="169"/>
+      <c r="AH4" s="169"/>
+      <c r="AI4" s="169"/>
+      <c r="AJ4" s="133"/>
+      <c r="AK4" s="164" t="s">
         <v>47</v>
       </c>
-      <c r="AL3" s="153"/>
-      <c r="AM3" s="153"/>
-      <c r="AN3" s="153"/>
-      <c r="AO3" s="148"/>
-    </row>
-    <row r="4" spans="1:41" ht="13.5" customHeight="1" thickTop="1">
-      <c r="A4" s="148" t="s">
+      <c r="AL4" s="166"/>
+      <c r="AM4" s="166"/>
+      <c r="AN4" s="166"/>
+      <c r="AO4" s="164"/>
+    </row>
+    <row r="5" spans="1:41" ht="13.5" customHeight="1" thickTop="1">
+      <c r="A5" s="164" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="148"/>
-      <c r="C4" s="149"/>
-      <c r="D4" s="148" t="s">
+      <c r="B5" s="164"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="148"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="148" t="s">
+      <c r="E5" s="164"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="164" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="148"/>
-      <c r="I4" s="149"/>
-      <c r="J4" s="148" t="s">
+      <c r="H5" s="164"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="164" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="151"/>
-      <c r="L4" s="151"/>
-      <c r="M4" s="151"/>
-      <c r="N4" s="151"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="148" t="s">
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="164" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="153"/>
-      <c r="R4" s="153"/>
-      <c r="S4" s="153"/>
-      <c r="U4" s="154"/>
-      <c r="V4" s="154"/>
-      <c r="W4" s="154"/>
-      <c r="X4" s="155"/>
-      <c r="Y4" s="154"/>
-      <c r="Z4" s="154"/>
-      <c r="AA4" s="156"/>
-      <c r="AB4" s="154"/>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="155"/>
-      <c r="AE4" s="157"/>
-      <c r="AF4" s="157"/>
-      <c r="AG4" s="157"/>
-      <c r="AH4" s="157"/>
-      <c r="AI4" s="157"/>
-      <c r="AJ4" s="158"/>
-      <c r="AK4" s="159"/>
-      <c r="AL4" s="159"/>
-      <c r="AM4" s="159"/>
-      <c r="AN4" s="159"/>
-      <c r="AO4" s="159"/>
-    </row>
-    <row r="5" spans="1:41" ht="13.5" customHeight="1">
-      <c r="A5" s="154"/>
-      <c r="B5" s="154"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="157"/>
-      <c r="N5" s="157"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="159"/>
-      <c r="Q5" s="159"/>
-      <c r="R5" s="159"/>
-      <c r="S5" s="159"/>
-      <c r="U5" s="154"/>
-      <c r="V5" s="154"/>
-      <c r="W5" s="154"/>
-      <c r="X5" s="155"/>
-      <c r="Y5" s="154"/>
-      <c r="Z5" s="154"/>
-      <c r="AA5" s="156"/>
-      <c r="AB5" s="154"/>
-      <c r="AC5" s="154"/>
-      <c r="AD5" s="155"/>
-      <c r="AE5" s="160" t="s">
+      <c r="Q5" s="166"/>
+      <c r="R5" s="166"/>
+      <c r="S5" s="166"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="162"/>
+      <c r="W5" s="162"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="162"/>
+      <c r="Z5" s="162"/>
+      <c r="AA5" s="135"/>
+      <c r="AB5" s="162"/>
+      <c r="AC5" s="162"/>
+      <c r="AD5" s="134"/>
+      <c r="AE5" s="161"/>
+      <c r="AF5" s="161"/>
+      <c r="AG5" s="161"/>
+      <c r="AH5" s="161"/>
+      <c r="AI5" s="161"/>
+      <c r="AJ5" s="136"/>
+      <c r="AK5" s="167"/>
+      <c r="AL5" s="167"/>
+      <c r="AM5" s="167"/>
+      <c r="AN5" s="167"/>
+      <c r="AO5" s="167"/>
+    </row>
+    <row r="6" spans="1:41" ht="13.5" customHeight="1">
+      <c r="A6" s="162"/>
+      <c r="B6" s="162"/>
+      <c r="C6" s="134"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="161"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="167"/>
+      <c r="Q6" s="167"/>
+      <c r="R6" s="167"/>
+      <c r="S6" s="167"/>
+      <c r="U6" s="162"/>
+      <c r="V6" s="162"/>
+      <c r="W6" s="162"/>
+      <c r="X6" s="134"/>
+      <c r="Y6" s="162"/>
+      <c r="Z6" s="162"/>
+      <c r="AA6" s="135"/>
+      <c r="AB6" s="162"/>
+      <c r="AC6" s="162"/>
+      <c r="AD6" s="134"/>
+      <c r="AE6" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="AF5" s="161"/>
-      <c r="AG5" s="162"/>
-      <c r="AH5" s="160" t="s">
+      <c r="AF6" s="160"/>
+      <c r="AG6" s="137"/>
+      <c r="AH6" s="159" t="s">
         <v>49</v>
       </c>
-      <c r="AI5" s="161"/>
-      <c r="AJ5" s="162"/>
-      <c r="AK5" s="154" t="s">
+      <c r="AI6" s="160"/>
+      <c r="AJ6" s="137"/>
+      <c r="AK6" s="162" t="s">
         <v>209</v>
       </c>
-      <c r="AL5" s="154"/>
-      <c r="AM5" s="162"/>
-      <c r="AN5" s="154" t="s">
+      <c r="AL6" s="162"/>
+      <c r="AM6" s="137"/>
+      <c r="AN6" s="162" t="s">
         <v>213</v>
       </c>
-      <c r="AO5" s="154"/>
-    </row>
-    <row r="6" spans="1:41" ht="12.75" customHeight="1">
-      <c r="A6" s="154"/>
-      <c r="B6" s="154"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="155"/>
-      <c r="J6" s="160" t="s">
+      <c r="AO6" s="162"/>
+    </row>
+    <row r="7" spans="1:41" ht="12.75" customHeight="1">
+      <c r="A7" s="162"/>
+      <c r="B7" s="162"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="161"/>
-      <c r="L6" s="162"/>
-      <c r="M6" s="160" t="s">
+      <c r="K7" s="160"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="159" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="161"/>
-      <c r="O6" s="162"/>
-      <c r="P6" s="154" t="s">
+      <c r="N7" s="160"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="Q6" s="154"/>
-      <c r="R6" s="162"/>
-      <c r="S6" s="154" t="s">
+      <c r="Q7" s="162"/>
+      <c r="R7" s="137"/>
+      <c r="S7" s="162" t="s">
         <v>51</v>
       </c>
-      <c r="U6" s="163"/>
-      <c r="V6" s="163"/>
-      <c r="W6" s="163"/>
-      <c r="X6" s="155"/>
-      <c r="Y6" s="163"/>
-      <c r="Z6" s="163"/>
-      <c r="AA6" s="156"/>
-      <c r="AB6" s="163"/>
-      <c r="AC6" s="163"/>
-      <c r="AD6" s="155"/>
-      <c r="AE6" s="157"/>
-      <c r="AF6" s="157"/>
-      <c r="AG6" s="164"/>
-      <c r="AH6" s="157"/>
-      <c r="AI6" s="157"/>
-      <c r="AJ6" s="162"/>
-      <c r="AK6" s="163"/>
-      <c r="AL6" s="163"/>
-      <c r="AM6" s="164"/>
-      <c r="AN6" s="165"/>
-      <c r="AO6" s="163"/>
-    </row>
-    <row r="7" spans="1:41" ht="12.75" customHeight="1">
-      <c r="A7" s="163"/>
-      <c r="B7" s="163"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="163"/>
-      <c r="E7" s="163"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="163"/>
-      <c r="H7" s="163"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="157"/>
-      <c r="K7" s="157"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="157"/>
-      <c r="N7" s="157"/>
-      <c r="O7" s="162"/>
-      <c r="P7" s="163"/>
-      <c r="Q7" s="163"/>
-      <c r="R7" s="164"/>
-      <c r="S7" s="165"/>
-    </row>
-    <row r="8" spans="1:41" ht="13.5">
-      <c r="V8" s="166" t="s">
+      <c r="U7" s="163"/>
+      <c r="V7" s="163"/>
+      <c r="W7" s="163"/>
+      <c r="X7" s="134"/>
+      <c r="Y7" s="163"/>
+      <c r="Z7" s="163"/>
+      <c r="AA7" s="135"/>
+      <c r="AB7" s="163"/>
+      <c r="AC7" s="163"/>
+      <c r="AD7" s="134"/>
+      <c r="AE7" s="161"/>
+      <c r="AF7" s="161"/>
+      <c r="AG7" s="138"/>
+      <c r="AH7" s="161"/>
+      <c r="AI7" s="161"/>
+      <c r="AJ7" s="137"/>
+      <c r="AK7" s="163"/>
+      <c r="AL7" s="163"/>
+      <c r="AM7" s="138"/>
+      <c r="AN7" s="165"/>
+      <c r="AO7" s="163"/>
+    </row>
+    <row r="8" spans="1:41" ht="12.75" customHeight="1">
+      <c r="A8" s="163"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="134"/>
+      <c r="J8" s="161"/>
+      <c r="K8" s="161"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="161"/>
+      <c r="N8" s="161"/>
+      <c r="O8" s="137"/>
+      <c r="P8" s="163"/>
+      <c r="Q8" s="163"/>
+      <c r="R8" s="138"/>
+      <c r="S8" s="165"/>
+    </row>
+    <row r="9" spans="1:41" ht="13.5">
+      <c r="V9" s="139" t="s">
         <v>161</v>
       </c>
-      <c r="W8" s="166"/>
-      <c r="Y8" s="167">
+      <c r="W9" s="139"/>
+      <c r="Y9" s="140">
         <v>0.41</v>
       </c>
-      <c r="Z8" s="168">
-        <f>Y8</f>
+      <c r="Z9" s="141">
+        <f>Y9</f>
         <v>0.41</v>
       </c>
-      <c r="AA8" s="169"/>
-      <c r="AB8" s="167">
+      <c r="AA9" s="142"/>
+      <c r="AB9" s="140">
         <v>0.43</v>
       </c>
-      <c r="AC8" s="168">
-        <f>AB8</f>
+      <c r="AC9" s="141">
+        <f>AB9</f>
         <v>0.43</v>
       </c>
-      <c r="AD8" s="170"/>
-      <c r="AE8" s="170">
+      <c r="AD9" s="143"/>
+      <c r="AE9" s="143">
         <v>-37</v>
       </c>
-      <c r="AF8" s="168">
-        <f>AE8</f>
+      <c r="AF9" s="141">
+        <f>AE9</f>
         <v>-37</v>
       </c>
-      <c r="AH8" s="167">
+      <c r="AH9" s="140">
         <v>-9.75</v>
       </c>
-      <c r="AI8" s="168">
-        <f>AH8</f>
+      <c r="AI9" s="141">
+        <f>AH9</f>
         <v>-9.75</v>
       </c>
-      <c r="AJ8" s="170"/>
-      <c r="AK8" s="167">
+      <c r="AJ9" s="143"/>
+      <c r="AK9" s="140">
         <v>0</v>
       </c>
-      <c r="AL8" s="168">
-        <f>AK8</f>
+      <c r="AL9" s="141">
+        <f>AK9</f>
         <v>0</v>
       </c>
-      <c r="AM8" s="169"/>
-      <c r="AN8" s="167">
+      <c r="AM9" s="142"/>
+      <c r="AN9" s="140">
         <v>0.41</v>
       </c>
-      <c r="AO8" s="168">
-        <f>AN8</f>
+      <c r="AO9" s="141">
+        <f>AN9</f>
         <v>0.41</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="13.5">
-      <c r="A9" s="166" t="s">
+    <row r="10" spans="1:41" ht="13.5">
+      <c r="A10" s="139" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="166"/>
-      <c r="D9" s="167">
+      <c r="B10" s="139"/>
+      <c r="D10" s="140">
         <v>0.41</v>
       </c>
-      <c r="E9" s="170"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="167">
+      <c r="E10" s="143"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="140">
         <v>0.43</v>
       </c>
-      <c r="H9" s="167"/>
-      <c r="I9" s="170"/>
-      <c r="J9" s="170">
+      <c r="H10" s="140"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143">
         <v>-37</v>
       </c>
-      <c r="K9" s="170"/>
-      <c r="M9" s="167">
+      <c r="K10" s="143"/>
+      <c r="M10" s="140">
         <v>-9.75</v>
       </c>
-      <c r="N9" s="170"/>
-      <c r="O9" s="170"/>
-      <c r="P9" s="167">
+      <c r="N10" s="143"/>
+      <c r="O10" s="143"/>
+      <c r="P10" s="140">
         <v>0</v>
       </c>
-      <c r="Q9" s="167"/>
-      <c r="R9" s="169"/>
-      <c r="S9" s="167">
+      <c r="Q10" s="140"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="140">
         <v>0.41</v>
       </c>
-      <c r="T9" s="167"/>
-      <c r="V9" s="171" t="s">
+      <c r="T10" s="140"/>
+      <c r="V10" s="144" t="s">
         <v>162</v>
       </c>
-      <c r="W9" s="171"/>
-      <c r="Y9" s="167">
+      <c r="W10" s="144"/>
+      <c r="Y10" s="140">
         <v>2.06</v>
       </c>
-      <c r="Z9" s="168">
-        <f t="shared" ref="Z9:Z20" si="0">Y9</f>
+      <c r="Z10" s="141">
+        <f t="shared" ref="Z10:Z21" si="0">Y10</f>
         <v>2.06</v>
       </c>
-      <c r="AA9" s="169"/>
-      <c r="AB9" s="167">
+      <c r="AA10" s="142"/>
+      <c r="AB10" s="140">
         <v>5.18</v>
       </c>
-      <c r="AC9" s="168">
-        <f t="shared" ref="AC9:AC20" si="1">AB9</f>
+      <c r="AC10" s="141">
+        <f t="shared" ref="AC10:AC21" si="1">AB10</f>
         <v>5.18</v>
       </c>
-      <c r="AD9" s="170"/>
-      <c r="AE9" s="170">
+      <c r="AD10" s="143"/>
+      <c r="AE10" s="143">
         <v>-437</v>
       </c>
-      <c r="AF9" s="168">
-        <f t="shared" ref="AF9:AF20" si="2">AE9</f>
+      <c r="AF10" s="141">
+        <f t="shared" ref="AF10:AF21" si="2">AE10</f>
         <v>-437</v>
       </c>
-      <c r="AH9" s="167">
+      <c r="AH10" s="140">
         <v>-19.07</v>
       </c>
-      <c r="AI9" s="168">
-        <f t="shared" ref="AI9:AI20" si="3">AH9</f>
+      <c r="AI10" s="141">
+        <f t="shared" ref="AI10:AI21" si="3">AH10</f>
         <v>-19.07</v>
       </c>
-      <c r="AJ9" s="170"/>
-      <c r="AK9" s="167">
+      <c r="AJ10" s="143"/>
+      <c r="AK10" s="140">
         <v>-0.27</v>
       </c>
-      <c r="AL9" s="168">
-        <f t="shared" ref="AL9:AL20" si="4">AK9</f>
+      <c r="AL10" s="141">
+        <f t="shared" ref="AL10:AL21" si="4">AK10</f>
         <v>-0.27</v>
       </c>
-      <c r="AM9" s="169"/>
-      <c r="AN9" s="167">
+      <c r="AM10" s="142"/>
+      <c r="AN10" s="140">
         <v>2.29</v>
       </c>
-      <c r="AO9" s="168">
-        <f t="shared" ref="AO9:AO20" si="5">AN9</f>
+      <c r="AO10" s="141">
+        <f t="shared" ref="AO10:AO21" si="5">AN10</f>
         <v>2.29</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="13.5">
-      <c r="A10" s="171" t="s">
+    <row r="11" spans="1:41" ht="13.5">
+      <c r="A11" s="144" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="171"/>
-      <c r="D10" s="167">
+      <c r="B11" s="144"/>
+      <c r="D11" s="140">
         <v>2.06</v>
       </c>
-      <c r="E10" s="170"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="167">
+      <c r="E11" s="143"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="140">
         <v>5.18</v>
       </c>
-      <c r="H10" s="167"/>
-      <c r="I10" s="170"/>
-      <c r="J10" s="170">
+      <c r="H11" s="140"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143">
         <v>-437</v>
       </c>
-      <c r="K10" s="170"/>
-      <c r="M10" s="167">
+      <c r="K11" s="143"/>
+      <c r="M11" s="140">
         <v>-19.07</v>
       </c>
-      <c r="N10" s="170"/>
-      <c r="O10" s="170"/>
-      <c r="P10" s="167">
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="140">
         <v>-0.27</v>
       </c>
-      <c r="Q10" s="167"/>
-      <c r="R10" s="169"/>
-      <c r="S10" s="167">
+      <c r="Q11" s="140"/>
+      <c r="R11" s="142"/>
+      <c r="S11" s="140">
         <v>2.29</v>
       </c>
-      <c r="T10" s="167"/>
-      <c r="V10" s="166" t="s">
+      <c r="T11" s="140"/>
+      <c r="V11" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="W10" s="166"/>
-      <c r="Y10" s="167">
+      <c r="W11" s="139"/>
+      <c r="Y11" s="140">
         <v>2.34</v>
       </c>
-      <c r="Z10" s="168">
+      <c r="Z11" s="141">
         <f t="shared" si="0"/>
         <v>2.34</v>
       </c>
-      <c r="AA10" s="169"/>
-      <c r="AB10" s="167">
+      <c r="AA11" s="142"/>
+      <c r="AB11" s="140">
         <v>9.66</v>
       </c>
-      <c r="AC10" s="168">
+      <c r="AC11" s="141">
         <f t="shared" si="1"/>
         <v>9.66</v>
       </c>
-      <c r="AD10" s="170"/>
-      <c r="AE10" s="170">
+      <c r="AD11" s="143"/>
+      <c r="AE11" s="143">
         <v>-814</v>
       </c>
-      <c r="AF10" s="168">
+      <c r="AF11" s="141">
         <f t="shared" si="2"/>
         <v>-814</v>
       </c>
-      <c r="AH10" s="167">
+      <c r="AH11" s="140">
         <v>-11.58</v>
       </c>
-      <c r="AI10" s="168">
+      <c r="AI11" s="141">
         <f t="shared" si="3"/>
         <v>-11.58</v>
       </c>
-      <c r="AJ10" s="170"/>
-      <c r="AK10" s="167">
+      <c r="AJ11" s="143"/>
+      <c r="AK11" s="140">
         <v>-0.19</v>
       </c>
-      <c r="AL10" s="168">
+      <c r="AL11" s="141">
         <f t="shared" si="4"/>
         <v>-0.19</v>
       </c>
-      <c r="AM10" s="169"/>
-      <c r="AN10" s="167">
+      <c r="AM11" s="142"/>
+      <c r="AN11" s="140">
         <v>7.68</v>
       </c>
-      <c r="AO10" s="168">
+      <c r="AO11" s="141">
         <f t="shared" si="5"/>
         <v>7.68</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="13.5">
-      <c r="A11" s="166" t="s">
+    <row r="12" spans="1:41" ht="13.5">
+      <c r="A12" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="166"/>
-      <c r="D11" s="167">
+      <c r="B12" s="139"/>
+      <c r="D12" s="140">
         <v>2.34</v>
       </c>
-      <c r="E11" s="170"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="167">
+      <c r="E12" s="143"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="140">
         <v>9.66</v>
       </c>
-      <c r="H11" s="167"/>
-      <c r="I11" s="170"/>
-      <c r="J11" s="170">
+      <c r="H12" s="140"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143">
         <v>-814</v>
       </c>
-      <c r="K11" s="170"/>
-      <c r="M11" s="167">
+      <c r="K12" s="143"/>
+      <c r="M12" s="140">
         <v>-11.58</v>
       </c>
-      <c r="N11" s="170"/>
-      <c r="O11" s="170"/>
-      <c r="P11" s="167">
+      <c r="N12" s="143"/>
+      <c r="O12" s="143"/>
+      <c r="P12" s="140">
         <v>-0.19</v>
       </c>
-      <c r="Q11" s="167"/>
-      <c r="R11" s="169"/>
-      <c r="S11" s="167">
+      <c r="Q12" s="140"/>
+      <c r="R12" s="142"/>
+      <c r="S12" s="140">
         <v>7.68</v>
       </c>
-      <c r="T11" s="167"/>
-      <c r="V11" s="166" t="s">
+      <c r="T12" s="140"/>
+      <c r="V12" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="W11" s="166"/>
-      <c r="Y11" s="167">
+      <c r="W12" s="139"/>
+      <c r="Y12" s="140">
         <v>2.27</v>
       </c>
-      <c r="Z11" s="168">
+      <c r="Z12" s="141">
         <f t="shared" si="0"/>
         <v>2.27</v>
       </c>
-      <c r="AA11" s="169"/>
-      <c r="AB11" s="167">
+      <c r="AA12" s="142"/>
+      <c r="AB12" s="140">
         <v>15.48</v>
       </c>
-      <c r="AC11" s="168">
+      <c r="AC12" s="141">
         <f t="shared" si="1"/>
         <v>15.48</v>
       </c>
-      <c r="AD11" s="170"/>
-      <c r="AE11" s="170">
+      <c r="AD12" s="143"/>
+      <c r="AE12" s="143">
         <v>-1305</v>
       </c>
-      <c r="AF11" s="168">
+      <c r="AF12" s="141">
         <f t="shared" si="2"/>
         <v>-1305</v>
       </c>
-      <c r="AH11" s="167">
+      <c r="AH12" s="140">
         <v>-8.41</v>
       </c>
-      <c r="AI11" s="168">
+      <c r="AI12" s="141">
         <f t="shared" si="3"/>
         <v>-8.41</v>
       </c>
-      <c r="AJ11" s="170"/>
-      <c r="AK11" s="167">
+      <c r="AJ12" s="143"/>
+      <c r="AK12" s="140">
         <v>0.2</v>
       </c>
-      <c r="AL11" s="168">
+      <c r="AL12" s="141">
         <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
-      <c r="AM11" s="169"/>
-      <c r="AN11" s="167">
+      <c r="AM12" s="142"/>
+      <c r="AN12" s="140">
         <v>17.559999999999999</v>
       </c>
-      <c r="AO11" s="168">
+      <c r="AO12" s="141">
         <f t="shared" si="5"/>
         <v>17.559999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="13.5">
-      <c r="A12" s="166" t="s">
+    <row r="13" spans="1:41" ht="13.5">
+      <c r="A13" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="166"/>
-      <c r="D12" s="167">
+      <c r="B13" s="139"/>
+      <c r="D13" s="140">
         <v>2.27</v>
       </c>
-      <c r="E12" s="170"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="167">
+      <c r="E13" s="143"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="140">
         <v>15.48</v>
       </c>
-      <c r="H12" s="167"/>
-      <c r="I12" s="170"/>
-      <c r="J12" s="170">
+      <c r="H13" s="140"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143">
         <v>-1305</v>
       </c>
-      <c r="K12" s="170"/>
-      <c r="M12" s="167">
+      <c r="K13" s="143"/>
+      <c r="M13" s="140">
         <v>-8.41</v>
       </c>
-      <c r="N12" s="170"/>
-      <c r="O12" s="170"/>
-      <c r="P12" s="167">
+      <c r="N13" s="143"/>
+      <c r="O13" s="143"/>
+      <c r="P13" s="140">
         <v>0.2</v>
       </c>
-      <c r="Q12" s="167"/>
-      <c r="R12" s="169"/>
-      <c r="S12" s="167">
+      <c r="Q13" s="140"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="140">
         <v>17.559999999999999</v>
       </c>
-      <c r="T12" s="167"/>
-      <c r="V12" s="166" t="s">
+      <c r="T13" s="140"/>
+      <c r="V13" s="139" t="s">
         <v>165</v>
       </c>
-      <c r="W12" s="166"/>
-      <c r="Y12" s="167">
+      <c r="W13" s="139"/>
+      <c r="Y13" s="140">
         <v>3.6</v>
       </c>
-      <c r="Z12" s="168">
+      <c r="Z13" s="141">
         <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
-      <c r="AA12" s="169"/>
-      <c r="AB12" s="167">
+      <c r="AA13" s="142"/>
+      <c r="AB13" s="140">
         <v>68.91</v>
       </c>
-      <c r="AC12" s="168">
+      <c r="AC13" s="141">
         <f t="shared" si="1"/>
         <v>68.91</v>
       </c>
-      <c r="AD12" s="170"/>
-      <c r="AE12" s="170">
+      <c r="AD13" s="143"/>
+      <c r="AE13" s="143">
         <v>-5809</v>
       </c>
-      <c r="AF12" s="168">
+      <c r="AF13" s="141">
         <f t="shared" si="2"/>
         <v>-5809</v>
       </c>
-      <c r="AH12" s="167">
+      <c r="AH13" s="140">
         <v>-9.07</v>
       </c>
-      <c r="AI12" s="168">
+      <c r="AI13" s="141">
         <f t="shared" si="3"/>
         <v>-9.07</v>
       </c>
-      <c r="AJ12" s="170"/>
-      <c r="AK12" s="167">
+      <c r="AJ13" s="143"/>
+      <c r="AK13" s="140">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AL12" s="168">
+      <c r="AL13" s="141">
         <f t="shared" si="4"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AM12" s="169"/>
-      <c r="AN12" s="167">
+      <c r="AM13" s="142"/>
+      <c r="AN13" s="140">
         <v>71.91</v>
       </c>
-      <c r="AO12" s="168">
+      <c r="AO13" s="141">
         <f t="shared" si="5"/>
         <v>71.91</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="13.5">
-      <c r="A13" s="166" t="s">
+    <row r="14" spans="1:41" ht="13.5">
+      <c r="A14" s="139" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="166"/>
-      <c r="D13" s="167">
+      <c r="B14" s="139"/>
+      <c r="D14" s="140">
         <v>3.6</v>
       </c>
-      <c r="E13" s="170"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="167">
+      <c r="E14" s="143"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="140">
         <v>68.91</v>
       </c>
-      <c r="H13" s="167"/>
-      <c r="I13" s="170"/>
-      <c r="J13" s="170">
+      <c r="H14" s="140"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143">
         <v>-5809</v>
       </c>
-      <c r="K13" s="170"/>
-      <c r="M13" s="167">
+      <c r="K14" s="143"/>
+      <c r="M14" s="140">
         <v>-9.07</v>
       </c>
-      <c r="N13" s="170"/>
-      <c r="O13" s="170"/>
-      <c r="P13" s="167">
+      <c r="N14" s="143"/>
+      <c r="O14" s="143"/>
+      <c r="P14" s="140">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q13" s="167"/>
-      <c r="R13" s="169"/>
-      <c r="S13" s="167">
+      <c r="Q14" s="140"/>
+      <c r="R14" s="142"/>
+      <c r="S14" s="140">
         <v>71.91</v>
       </c>
-      <c r="T13" s="167"/>
-      <c r="V13" s="166" t="s">
+      <c r="T14" s="140"/>
+      <c r="V14" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="W13" s="166"/>
-      <c r="Y13" s="167">
+      <c r="W14" s="139"/>
+      <c r="Y14" s="140">
         <v>2.99</v>
       </c>
-      <c r="Z13" s="168">
+      <c r="Z14" s="141">
         <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
-      <c r="AA13" s="169"/>
-      <c r="AB13" s="167">
+      <c r="AA14" s="142"/>
+      <c r="AB14" s="140">
         <v>100</v>
       </c>
-      <c r="AC13" s="168">
+      <c r="AC14" s="141">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AD13" s="170"/>
-      <c r="AE13" s="170">
+      <c r="AD14" s="143"/>
+      <c r="AE14" s="143">
         <v>-1686</v>
       </c>
-      <c r="AF13" s="168">
+      <c r="AF14" s="141">
         <f t="shared" si="2"/>
         <v>-1686</v>
       </c>
-      <c r="AH13" s="167">
+      <c r="AH14" s="140">
         <v>-9.43</v>
       </c>
-      <c r="AI13" s="168">
+      <c r="AI14" s="141">
         <f t="shared" si="3"/>
         <v>-9.43</v>
       </c>
-      <c r="AJ13" s="170"/>
-      <c r="AK13" s="167">
+      <c r="AJ14" s="143"/>
+      <c r="AK14" s="140">
         <v>0</v>
       </c>
-      <c r="AL13" s="168">
+      <c r="AL14" s="141">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AM13" s="169"/>
-      <c r="AN13" s="167">
+      <c r="AM14" s="142"/>
+      <c r="AN14" s="140">
         <v>100</v>
       </c>
-      <c r="AO13" s="168">
+      <c r="AO14" s="141">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="13.5">
-      <c r="A14" s="166" t="s">
+    <row r="15" spans="1:41" ht="13.5">
+      <c r="A15" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="166"/>
-      <c r="D14" s="167">
+      <c r="B15" s="139"/>
+      <c r="D15" s="140">
         <v>2.99</v>
       </c>
-      <c r="E14" s="170"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="167">
+      <c r="E15" s="143"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="140">
         <v>100</v>
       </c>
-      <c r="H14" s="167"/>
-      <c r="I14" s="170"/>
-      <c r="J14" s="170">
+      <c r="H15" s="140"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143">
         <v>-1686</v>
       </c>
-      <c r="K14" s="170"/>
-      <c r="M14" s="167">
+      <c r="K15" s="143"/>
+      <c r="M15" s="140">
         <v>-9.43</v>
       </c>
-      <c r="N14" s="170"/>
-      <c r="O14" s="170"/>
-      <c r="P14" s="167">
+      <c r="N15" s="143"/>
+      <c r="O15" s="143"/>
+      <c r="P15" s="140">
         <v>0</v>
       </c>
-      <c r="Q14" s="167"/>
-      <c r="R14" s="169"/>
-      <c r="S14" s="167">
+      <c r="Q15" s="140"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="140">
         <v>100</v>
       </c>
-      <c r="T14" s="167"/>
-      <c r="V14" s="166"/>
-      <c r="W14" s="166"/>
-      <c r="Y14" s="167"/>
-      <c r="Z14" s="168"/>
-      <c r="AA14" s="169"/>
-      <c r="AB14" s="167"/>
-      <c r="AC14" s="168"/>
-      <c r="AD14" s="170"/>
-      <c r="AE14" s="170"/>
-      <c r="AF14" s="168"/>
-      <c r="AH14" s="167"/>
-      <c r="AI14" s="168"/>
-      <c r="AJ14" s="170"/>
-      <c r="AK14" s="167"/>
-      <c r="AL14" s="168"/>
-      <c r="AM14" s="169"/>
-      <c r="AN14" s="167"/>
-      <c r="AO14" s="168"/>
-    </row>
-    <row r="15" spans="1:41" ht="13.5">
-      <c r="A15" s="166"/>
-      <c r="B15" s="166"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="170"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="167"/>
-      <c r="H15" s="167"/>
-      <c r="I15" s="170"/>
-      <c r="J15" s="170"/>
-      <c r="K15" s="170"/>
-      <c r="M15" s="167"/>
-      <c r="N15" s="170"/>
-      <c r="O15" s="170"/>
-      <c r="P15" s="167"/>
-      <c r="Q15" s="167"/>
-      <c r="R15" s="169"/>
-      <c r="S15" s="167"/>
-      <c r="T15" s="167"/>
-      <c r="V15" s="172" t="s">
+      <c r="T15" s="140"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="Y15" s="140"/>
+      <c r="Z15" s="141"/>
+      <c r="AA15" s="142"/>
+      <c r="AB15" s="140"/>
+      <c r="AC15" s="141"/>
+      <c r="AD15" s="143"/>
+      <c r="AE15" s="143"/>
+      <c r="AF15" s="141"/>
+      <c r="AH15" s="140"/>
+      <c r="AI15" s="141"/>
+      <c r="AJ15" s="143"/>
+      <c r="AK15" s="140"/>
+      <c r="AL15" s="141"/>
+      <c r="AM15" s="142"/>
+      <c r="AN15" s="140"/>
+      <c r="AO15" s="141"/>
+    </row>
+    <row r="16" spans="1:41" ht="13.5">
+      <c r="A16" s="139"/>
+      <c r="B16" s="139"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="142"/>
+      <c r="S16" s="140"/>
+      <c r="T16" s="140"/>
+      <c r="V16" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="W15" s="166"/>
-      <c r="Z15" s="168"/>
-      <c r="AC15" s="168"/>
-      <c r="AF15" s="168"/>
-      <c r="AI15" s="168"/>
-      <c r="AL15" s="168"/>
-      <c r="AM15" s="169"/>
-      <c r="AO15" s="168"/>
-    </row>
-    <row r="16" spans="1:41" ht="13.5">
-      <c r="A16" s="172" t="s">
+      <c r="W16" s="139"/>
+      <c r="Z16" s="141"/>
+      <c r="AC16" s="141"/>
+      <c r="AF16" s="141"/>
+      <c r="AI16" s="141"/>
+      <c r="AL16" s="141"/>
+      <c r="AM16" s="142"/>
+      <c r="AO16" s="141"/>
+    </row>
+    <row r="17" spans="1:41" ht="13.5">
+      <c r="A17" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="166"/>
-      <c r="Q16" s="167"/>
-      <c r="R16" s="169"/>
-      <c r="V16" s="166" t="s">
+      <c r="B17" s="139"/>
+      <c r="Q17" s="140"/>
+      <c r="R17" s="142"/>
+      <c r="V17" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="W16" s="166"/>
-      <c r="Y16" s="167">
+      <c r="W17" s="139"/>
+      <c r="Y17" s="140">
         <v>4.03</v>
       </c>
-      <c r="Z16" s="168">
+      <c r="Z17" s="141">
         <f t="shared" si="0"/>
         <v>4.03</v>
       </c>
-      <c r="AA16" s="169"/>
-      <c r="AB16" s="167">
+      <c r="AA17" s="142"/>
+      <c r="AB17" s="140">
         <v>56.09</v>
       </c>
-      <c r="AC16" s="168">
+      <c r="AC17" s="141">
         <f t="shared" si="1"/>
         <v>56.09</v>
       </c>
-      <c r="AD16" s="170"/>
-      <c r="AE16" s="170">
+      <c r="AD17" s="143"/>
+      <c r="AE17" s="143">
         <v>-9457</v>
       </c>
-      <c r="AF16" s="168">
+      <c r="AF17" s="141">
         <f t="shared" si="2"/>
         <v>-9457</v>
       </c>
-      <c r="AH16" s="167">
+      <c r="AH17" s="140">
         <v>-9.4600000000000009</v>
       </c>
-      <c r="AI16" s="168">
+      <c r="AI17" s="141">
         <f t="shared" si="3"/>
         <v>-9.4600000000000009</v>
       </c>
-      <c r="AJ16" s="170"/>
-      <c r="AK16" s="167">
+      <c r="AJ17" s="143"/>
+      <c r="AK17" s="140">
         <v>-0.02</v>
       </c>
-      <c r="AL16" s="168">
+      <c r="AL17" s="141">
         <f t="shared" si="4"/>
         <v>-0.02</v>
       </c>
-      <c r="AM16" s="169"/>
-      <c r="AN16" s="167">
+      <c r="AM17" s="142"/>
+      <c r="AN17" s="140">
         <v>55.87</v>
       </c>
-      <c r="AO16" s="168">
+      <c r="AO17" s="141">
         <f t="shared" si="5"/>
         <v>55.87</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="13.5">
-      <c r="A17" s="166" t="s">
+    <row r="18" spans="1:41" ht="13.5">
+      <c r="A18" s="139" t="s">
         <v>166</v>
       </c>
-      <c r="B17" s="166"/>
-      <c r="D17" s="167">
+      <c r="B18" s="139"/>
+      <c r="D18" s="140">
         <v>4.03</v>
       </c>
-      <c r="E17" s="170"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="167">
+      <c r="E18" s="143"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="140">
         <v>56.09</v>
       </c>
-      <c r="H17" s="167"/>
-      <c r="I17" s="170"/>
-      <c r="J17" s="170">
+      <c r="H18" s="140"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="143">
         <v>-9457</v>
       </c>
-      <c r="K17" s="170"/>
-      <c r="M17" s="167">
+      <c r="K18" s="143"/>
+      <c r="M18" s="140">
         <v>-9.4600000000000009</v>
       </c>
-      <c r="N17" s="170"/>
-      <c r="O17" s="170"/>
-      <c r="P17" s="167">
+      <c r="N18" s="143"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="140">
         <v>-0.02</v>
       </c>
-      <c r="Q17" s="167"/>
-      <c r="R17" s="169"/>
-      <c r="S17" s="167">
+      <c r="Q18" s="140"/>
+      <c r="R18" s="142"/>
+      <c r="S18" s="140">
         <v>55.87</v>
       </c>
-      <c r="T17" s="167"/>
-      <c r="V17" s="166" t="s">
+      <c r="T18" s="140"/>
+      <c r="V18" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="W17" s="166"/>
-      <c r="Y17" s="167">
+      <c r="W18" s="139"/>
+      <c r="Y18" s="140">
         <v>4.68</v>
       </c>
-      <c r="Z17" s="168">
+      <c r="Z18" s="141">
         <f t="shared" si="0"/>
         <v>4.68</v>
       </c>
-      <c r="AA17" s="169"/>
-      <c r="AB17" s="167">
+      <c r="AA18" s="142"/>
+      <c r="AB18" s="140">
         <v>48.1</v>
       </c>
-      <c r="AC17" s="168">
+      <c r="AC18" s="141">
         <f t="shared" si="1"/>
         <v>48.1</v>
       </c>
-      <c r="AD17" s="170"/>
-      <c r="AE17" s="170">
+      <c r="AD18" s="143"/>
+      <c r="AE18" s="143">
         <v>-16223</v>
       </c>
-      <c r="AF17" s="168">
+      <c r="AF18" s="141">
         <f t="shared" si="2"/>
         <v>-16223</v>
       </c>
-      <c r="AH17" s="167">
+      <c r="AH18" s="140">
         <v>-10.39</v>
       </c>
-      <c r="AI17" s="168">
+      <c r="AI18" s="141">
         <f t="shared" si="3"/>
         <v>-10.39</v>
       </c>
-      <c r="AJ17" s="170"/>
-      <c r="AK17" s="167">
+      <c r="AJ18" s="143"/>
+      <c r="AK18" s="140">
         <v>-0.46</v>
       </c>
-      <c r="AL17" s="168">
+      <c r="AL18" s="141">
         <f t="shared" si="4"/>
         <v>-0.46</v>
       </c>
-      <c r="AM17" s="169"/>
-      <c r="AN17" s="167">
+      <c r="AM18" s="142"/>
+      <c r="AN18" s="140">
         <v>43.22</v>
       </c>
-      <c r="AO17" s="168">
+      <c r="AO18" s="141">
         <f t="shared" si="5"/>
         <v>43.22</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="13.5">
-      <c r="A18" s="166" t="s">
+    <row r="19" spans="1:41" ht="13.5">
+      <c r="A19" s="139" t="s">
         <v>167</v>
       </c>
-      <c r="B18" s="166"/>
-      <c r="D18" s="167">
+      <c r="B19" s="139"/>
+      <c r="D19" s="140">
         <v>4.68</v>
       </c>
-      <c r="E18" s="170"/>
-      <c r="F18" s="169"/>
-      <c r="G18" s="167">
+      <c r="E19" s="143"/>
+      <c r="F19" s="142"/>
+      <c r="G19" s="140">
         <v>48.1</v>
       </c>
-      <c r="H18" s="167"/>
-      <c r="I18" s="170"/>
-      <c r="J18" s="170">
+      <c r="H19" s="140"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="143">
         <v>-16223</v>
       </c>
-      <c r="K18" s="170"/>
-      <c r="M18" s="167">
+      <c r="K19" s="143"/>
+      <c r="M19" s="140">
         <v>-10.39</v>
       </c>
-      <c r="N18" s="170"/>
-      <c r="O18" s="170"/>
-      <c r="P18" s="167">
+      <c r="N19" s="143"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="140">
         <v>-0.46</v>
       </c>
-      <c r="Q18" s="167"/>
-      <c r="R18" s="169"/>
-      <c r="S18" s="167">
+      <c r="Q19" s="140"/>
+      <c r="R19" s="142"/>
+      <c r="S19" s="140">
         <v>43.22</v>
       </c>
-      <c r="T18" s="167"/>
-      <c r="V18" s="166" t="s">
+      <c r="T19" s="140"/>
+      <c r="V19" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="W18" s="166"/>
-      <c r="Y18" s="167">
+      <c r="W19" s="139"/>
+      <c r="Y19" s="140">
         <v>6.74</v>
       </c>
-      <c r="Z18" s="168">
+      <c r="Z19" s="141">
         <f t="shared" si="0"/>
         <v>6.74</v>
       </c>
-      <c r="AA18" s="169"/>
-      <c r="AB18" s="167">
+      <c r="AA19" s="142"/>
+      <c r="AB19" s="140">
         <v>36.78</v>
       </c>
-      <c r="AC18" s="168">
+      <c r="AC19" s="141">
         <f t="shared" si="1"/>
         <v>36.78</v>
       </c>
-      <c r="AD18" s="170"/>
-      <c r="AE18" s="170">
+      <c r="AD19" s="143"/>
+      <c r="AE19" s="143">
         <v>-62007</v>
       </c>
-      <c r="AF18" s="168">
+      <c r="AF19" s="141">
         <f t="shared" si="2"/>
         <v>-62007</v>
       </c>
-      <c r="AH18" s="167">
+      <c r="AH19" s="140">
         <v>-13.37</v>
       </c>
-      <c r="AI18" s="168">
+      <c r="AI19" s="141">
         <f t="shared" si="3"/>
         <v>-13.37</v>
       </c>
-      <c r="AJ18" s="170"/>
-      <c r="AK18" s="167">
+      <c r="AJ19" s="143"/>
+      <c r="AK19" s="140">
         <v>-1.1299999999999999</v>
       </c>
-      <c r="AL18" s="168">
+      <c r="AL19" s="141">
         <f t="shared" si="4"/>
         <v>-1.1299999999999999</v>
       </c>
-      <c r="AM18" s="169"/>
-      <c r="AN18" s="167">
+      <c r="AM19" s="142"/>
+      <c r="AN19" s="140">
         <v>24.83</v>
       </c>
-      <c r="AO18" s="168">
+      <c r="AO19" s="141">
         <f t="shared" si="5"/>
         <v>24.83</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="13.5">
-      <c r="A19" s="166" t="s">
+    <row r="20" spans="1:41" ht="13.5">
+      <c r="A20" s="139" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="166"/>
-      <c r="D19" s="167">
+      <c r="B20" s="139"/>
+      <c r="D20" s="140">
         <v>6.74</v>
       </c>
-      <c r="E19" s="170"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="167">
+      <c r="E20" s="143"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="140">
         <v>36.78</v>
       </c>
-      <c r="H19" s="167"/>
-      <c r="I19" s="170"/>
-      <c r="J19" s="170">
+      <c r="H20" s="140"/>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143">
         <v>-62007</v>
       </c>
-      <c r="K19" s="170"/>
-      <c r="M19" s="167">
+      <c r="K20" s="143"/>
+      <c r="M20" s="140">
         <v>-13.37</v>
       </c>
-      <c r="N19" s="170"/>
-      <c r="O19" s="170"/>
-      <c r="P19" s="167">
+      <c r="N20" s="143"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="140">
         <v>-1.1299999999999999</v>
       </c>
-      <c r="Q19" s="167"/>
-      <c r="R19" s="169"/>
-      <c r="S19" s="167">
+      <c r="Q20" s="140"/>
+      <c r="R20" s="142"/>
+      <c r="S20" s="140">
         <v>24.83</v>
       </c>
-      <c r="T19" s="167"/>
-      <c r="V19" s="166" t="s">
+      <c r="T20" s="140"/>
+      <c r="V20" s="139" t="s">
         <v>169</v>
       </c>
-      <c r="W19" s="166"/>
-      <c r="Y19" s="167">
+      <c r="W20" s="139"/>
+      <c r="Y20" s="140">
         <v>7.33</v>
       </c>
-      <c r="Z19" s="168">
+      <c r="Z20" s="141">
         <f t="shared" si="0"/>
         <v>7.33</v>
       </c>
-      <c r="AA19" s="169"/>
-      <c r="AB19" s="167">
+      <c r="AA20" s="142"/>
+      <c r="AB20" s="140">
         <v>31.05</v>
       </c>
-      <c r="AC19" s="168">
+      <c r="AC20" s="141">
         <f t="shared" si="1"/>
         <v>31.05</v>
       </c>
-      <c r="AD19" s="170"/>
-      <c r="AE19" s="170">
+      <c r="AD20" s="143"/>
+      <c r="AE20" s="143">
         <v>-104678</v>
       </c>
-      <c r="AF19" s="168">
+      <c r="AF20" s="141">
         <f t="shared" si="2"/>
         <v>-104678</v>
       </c>
-      <c r="AH19" s="167">
+      <c r="AH20" s="140">
         <v>-13.91</v>
       </c>
-      <c r="AI19" s="168">
+      <c r="AI20" s="141">
         <f t="shared" si="3"/>
         <v>-13.91</v>
       </c>
-      <c r="AJ19" s="170"/>
-      <c r="AK19" s="167">
+      <c r="AJ20" s="143"/>
+      <c r="AK20" s="140">
         <v>-1.04</v>
       </c>
-      <c r="AL19" s="168">
+      <c r="AL20" s="141">
         <f t="shared" si="4"/>
         <v>-1.04</v>
       </c>
-      <c r="AM19" s="169"/>
-      <c r="AN19" s="167">
+      <c r="AM20" s="142"/>
+      <c r="AN20" s="140">
         <v>20.010000000000002</v>
       </c>
-      <c r="AO19" s="168">
+      <c r="AO20" s="141">
         <f t="shared" si="5"/>
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="13.5">
-      <c r="A20" s="166" t="s">
+    <row r="21" spans="1:41" ht="13.5">
+      <c r="A21" s="139" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="166"/>
-      <c r="D20" s="167">
+      <c r="B21" s="139"/>
+      <c r="D21" s="140">
         <v>7.33</v>
       </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="167">
+      <c r="E21" s="143"/>
+      <c r="F21" s="142"/>
+      <c r="G21" s="140">
         <v>31.05</v>
       </c>
-      <c r="H20" s="167"/>
-      <c r="I20" s="170"/>
-      <c r="J20" s="170">
+      <c r="H21" s="140"/>
+      <c r="I21" s="143"/>
+      <c r="J21" s="143">
         <v>-104678</v>
       </c>
-      <c r="K20" s="170"/>
-      <c r="M20" s="167">
+      <c r="K21" s="143"/>
+      <c r="M21" s="140">
         <v>-13.91</v>
       </c>
-      <c r="N20" s="170"/>
-      <c r="O20" s="170"/>
-      <c r="P20" s="167">
+      <c r="N21" s="143"/>
+      <c r="O21" s="143"/>
+      <c r="P21" s="140">
         <v>-1.04</v>
       </c>
-      <c r="Q20" s="167"/>
-      <c r="R20" s="169"/>
-      <c r="S20" s="167">
+      <c r="Q21" s="140"/>
+      <c r="R21" s="142"/>
+      <c r="S21" s="140">
         <v>20.010000000000002</v>
       </c>
-      <c r="T20" s="167"/>
-      <c r="V20" s="166" t="s">
+      <c r="T21" s="140"/>
+      <c r="V21" s="139" t="s">
         <v>170</v>
       </c>
-      <c r="W20" s="166"/>
-      <c r="Y20" s="167">
+      <c r="W21" s="139"/>
+      <c r="Y21" s="140">
         <v>7.81</v>
       </c>
-      <c r="Z20" s="168">
+      <c r="Z21" s="141">
         <f t="shared" si="0"/>
         <v>7.81</v>
       </c>
-      <c r="AA20" s="169"/>
-      <c r="AB20" s="167">
+      <c r="AA21" s="142"/>
+      <c r="AB21" s="140">
         <v>18.63</v>
       </c>
-      <c r="AC20" s="168">
+      <c r="AC21" s="141">
         <f t="shared" si="1"/>
         <v>18.63</v>
       </c>
-      <c r="AD20" s="170"/>
-      <c r="AE20" s="170">
+      <c r="AD21" s="143"/>
+      <c r="AE21" s="143">
         <v>-314150</v>
       </c>
-      <c r="AF20" s="168">
+      <c r="AF21" s="141">
         <f t="shared" si="2"/>
         <v>-314150</v>
       </c>
-      <c r="AH20" s="167">
+      <c r="AH21" s="140">
         <v>-13.68</v>
       </c>
-      <c r="AI20" s="168">
+      <c r="AI21" s="141">
         <f t="shared" si="3"/>
         <v>-13.68</v>
       </c>
-      <c r="AJ20" s="170"/>
-      <c r="AK20" s="167">
+      <c r="AJ21" s="143"/>
+      <c r="AK21" s="140">
         <v>-0.6</v>
       </c>
-      <c r="AL20" s="168">
+      <c r="AL21" s="141">
         <f t="shared" si="4"/>
         <v>-0.6</v>
       </c>
-      <c r="AM20" s="169"/>
-      <c r="AN20" s="167">
+      <c r="AM21" s="142"/>
+      <c r="AN21" s="140">
         <v>12.25</v>
       </c>
-      <c r="AO20" s="168">
+      <c r="AO21" s="141">
         <f t="shared" si="5"/>
         <v>12.25</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="13.5">
-      <c r="A21" s="166" t="s">
+    <row r="22" spans="1:41" ht="13.5">
+      <c r="A22" s="139" t="s">
         <v>170</v>
       </c>
-      <c r="B21" s="166"/>
-      <c r="D21" s="167">
+      <c r="B22" s="139"/>
+      <c r="D22" s="140">
         <v>7.81</v>
       </c>
-      <c r="E21" s="170"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="167">
+      <c r="E22" s="143"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="140">
         <v>18.63</v>
       </c>
-      <c r="H21" s="167"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="170">
+      <c r="H22" s="140"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143">
         <v>-314150</v>
       </c>
-      <c r="K21" s="170"/>
-      <c r="M21" s="167">
+      <c r="K22" s="143"/>
+      <c r="M22" s="140">
         <v>-13.68</v>
       </c>
-      <c r="N21" s="170"/>
-      <c r="O21" s="170"/>
-      <c r="P21" s="167">
+      <c r="N22" s="143"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="140">
         <v>-0.6</v>
       </c>
-      <c r="Q21" s="167"/>
-      <c r="R21" s="169"/>
-      <c r="S21" s="167">
+      <c r="Q22" s="140"/>
+      <c r="R22" s="142"/>
+      <c r="S22" s="140">
         <v>12.25</v>
       </c>
-      <c r="T21" s="167"/>
-      <c r="U21" s="173"/>
-      <c r="V21" s="173"/>
-      <c r="W21" s="173"/>
-      <c r="X21" s="173"/>
-      <c r="Y21" s="173"/>
-      <c r="Z21" s="173"/>
-      <c r="AA21" s="173"/>
-      <c r="AB21" s="173"/>
-      <c r="AC21" s="173"/>
-      <c r="AD21" s="173"/>
-      <c r="AE21" s="173"/>
-      <c r="AF21" s="173"/>
-      <c r="AG21" s="173"/>
-      <c r="AH21" s="173"/>
-      <c r="AI21" s="173"/>
-      <c r="AJ21" s="173"/>
-      <c r="AK21" s="173"/>
-      <c r="AL21" s="173"/>
-      <c r="AM21" s="173"/>
-      <c r="AN21" s="173"/>
-      <c r="AO21" s="173"/>
-    </row>
-    <row r="22" spans="1:41" ht="13.5">
-      <c r="A22" s="173"/>
-      <c r="B22" s="173"/>
-      <c r="C22" s="173"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="173"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="173"/>
-      <c r="L22" s="173"/>
-      <c r="M22" s="173"/>
-      <c r="N22" s="173"/>
-      <c r="O22" s="173"/>
-      <c r="P22" s="173"/>
-      <c r="Q22" s="173"/>
-      <c r="R22" s="173"/>
-      <c r="S22" s="173"/>
-      <c r="U22" s="146" t="s">
+      <c r="T22" s="140"/>
+      <c r="U22" s="146"/>
+      <c r="V22" s="146"/>
+      <c r="W22" s="146"/>
+      <c r="X22" s="146"/>
+      <c r="Y22" s="146"/>
+      <c r="Z22" s="146"/>
+      <c r="AA22" s="146"/>
+      <c r="AB22" s="146"/>
+      <c r="AC22" s="146"/>
+      <c r="AD22" s="146"/>
+      <c r="AE22" s="146"/>
+      <c r="AF22" s="146"/>
+      <c r="AG22" s="146"/>
+      <c r="AH22" s="146"/>
+      <c r="AI22" s="146"/>
+      <c r="AJ22" s="146"/>
+      <c r="AK22" s="146"/>
+      <c r="AL22" s="146"/>
+      <c r="AM22" s="146"/>
+      <c r="AN22" s="146"/>
+      <c r="AO22" s="146"/>
+    </row>
+    <row r="23" spans="1:41" ht="13.5">
+      <c r="A23" s="146"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="146"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="146"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="146"/>
+      <c r="P23" s="146"/>
+      <c r="Q23" s="146"/>
+      <c r="R23" s="146"/>
+      <c r="S23" s="146"/>
+      <c r="U23" s="129" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="13.5">
-      <c r="A23" s="146" t="s">
+    <row r="24" spans="1:41" ht="13.5">
+      <c r="A24" s="129" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:41" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="J6:K7"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="P6:Q7"/>
-    <mergeCell ref="U3:U6"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="AE5:AF6"/>
-    <mergeCell ref="AH5:AI6"/>
-    <mergeCell ref="AK5:AL6"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="P4:S5"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AO6:AO7"/>
     <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="D4:E7"/>
-    <mergeCell ref="G4:H7"/>
-    <mergeCell ref="J4:N5"/>
-    <mergeCell ref="V1:AN1"/>
-    <mergeCell ref="V3:W6"/>
-    <mergeCell ref="Y3:Z6"/>
-    <mergeCell ref="AB3:AC6"/>
-    <mergeCell ref="AE3:AI4"/>
-    <mergeCell ref="AK3:AN4"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A5:B8"/>
+    <mergeCell ref="D5:E8"/>
+    <mergeCell ref="G5:H8"/>
+    <mergeCell ref="J5:N6"/>
+    <mergeCell ref="V2:AN2"/>
+    <mergeCell ref="V4:W7"/>
+    <mergeCell ref="Y4:Z7"/>
+    <mergeCell ref="AB4:AC7"/>
+    <mergeCell ref="AE4:AI5"/>
+    <mergeCell ref="AK4:AN5"/>
+    <mergeCell ref="AE6:AF7"/>
+    <mergeCell ref="AH6:AI7"/>
+    <mergeCell ref="AK6:AL7"/>
+    <mergeCell ref="AN6:AN7"/>
+    <mergeCell ref="P5:S6"/>
+    <mergeCell ref="J7:K8"/>
+    <mergeCell ref="M7:N8"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="U4:U7"/>
+    <mergeCell ref="S7:S8"/>
   </mergeCells>
   <phoneticPr fontId="27" type="noConversion"/>
-  <conditionalFormatting sqref="Z8:Z20">
+  <conditionalFormatting sqref="Z9:Z21">
     <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
@@ -42527,7 +43740,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC8:AC20">
+  <conditionalFormatting sqref="AC9:AC21">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="min"/>
@@ -42541,7 +43754,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF8:AF20">
+  <conditionalFormatting sqref="AF9:AF21">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -42555,7 +43768,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI8:AI20">
+  <conditionalFormatting sqref="AI9:AI21">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -42569,7 +43782,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL8:AL20">
+  <conditionalFormatting sqref="AL9:AL21">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -42583,7 +43796,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO8:AO20">
+  <conditionalFormatting sqref="AO9:AO21">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -42612,7 +43825,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Z8:Z20</xm:sqref>
+          <xm:sqref>Z9:Z21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1F00E25A-75AC-F44C-B09C-2AB0F64A5F24}">
@@ -42623,7 +43836,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AC8:AC20</xm:sqref>
+          <xm:sqref>AC9:AC21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1BEBD3AF-E1E8-9E4D-ADA5-A0A63BE778A1}">
@@ -42634,7 +43847,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AF8:AF20</xm:sqref>
+          <xm:sqref>AF9:AF21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{BB6A81F1-2B45-D446-8F14-721F4A5E6834}">
@@ -42645,7 +43858,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AI8:AI20</xm:sqref>
+          <xm:sqref>AI9:AI21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{EDD0FB12-98B8-2E4F-9676-F41FA7F7266D}">
@@ -42656,7 +43869,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AL8:AL20</xm:sqref>
+          <xm:sqref>AL9:AL21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{065D418A-0D6D-F144-A2D8-688518C4F69C}">
@@ -42667,7 +43880,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AO8:AO20</xm:sqref>
+          <xm:sqref>AO9:AO21</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -43447,35 +44660,35 @@
       <c r="A40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="62" t="s">
+      <c r="B40" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="63"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
-      <c r="G40" s="63"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="63"/>
-      <c r="K40" s="63"/>
+      <c r="C40" s="171"/>
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
+      <c r="F40" s="171"/>
+      <c r="G40" s="171"/>
+      <c r="H40" s="171"/>
+      <c r="I40" s="171"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="171"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
+      <c r="C41" s="172"/>
+      <c r="D41" s="172"/>
+      <c r="E41" s="172"/>
+      <c r="F41" s="172"/>
+      <c r="G41" s="172"/>
+      <c r="H41" s="172"/>
+      <c r="I41" s="172"/>
+      <c r="J41" s="172"/>
+      <c r="K41" s="172"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="8"/>
@@ -43544,16 +44757,16 @@
       <c r="A5" s="32">
         <v>1975</v>
       </c>
-      <c r="B5" s="175">
+      <c r="B5" s="147">
         <v>3.3724907063197027</v>
       </c>
-      <c r="C5" s="175">
+      <c r="C5" s="147">
         <v>1.3115241635687733</v>
       </c>
-      <c r="D5" s="175">
+      <c r="D5" s="147">
         <v>0</v>
       </c>
-      <c r="E5" s="175">
+      <c r="E5" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43561,16 +44774,16 @@
       <c r="A6" s="32">
         <v>1976</v>
       </c>
-      <c r="B6" s="175">
+      <c r="B6" s="147">
         <v>3.1533216168717049</v>
       </c>
-      <c r="C6" s="175">
+      <c r="C6" s="147">
         <v>1.43493848857645</v>
       </c>
-      <c r="D6" s="175">
+      <c r="D6" s="147">
         <v>0</v>
       </c>
-      <c r="E6" s="175">
+      <c r="E6" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43578,16 +44791,16 @@
       <c r="A7" s="32">
         <v>1977</v>
       </c>
-      <c r="B7" s="175">
+      <c r="B7" s="147">
         <v>2.9275247524752475</v>
       </c>
-      <c r="C7" s="175">
+      <c r="C7" s="147">
         <v>0.82170297029702954</v>
       </c>
-      <c r="D7" s="175">
+      <c r="D7" s="147">
         <v>0</v>
       </c>
-      <c r="E7" s="175">
+      <c r="E7" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43595,16 +44808,16 @@
       <c r="A8" s="32">
         <v>1978</v>
       </c>
-      <c r="B8" s="175">
+      <c r="B8" s="147">
         <v>2.4767116564417173</v>
       </c>
-      <c r="C8" s="175">
+      <c r="C8" s="147">
         <v>0.76373006134969323</v>
       </c>
-      <c r="D8" s="175">
+      <c r="D8" s="147">
         <v>0</v>
       </c>
-      <c r="E8" s="175">
+      <c r="E8" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43612,16 +44825,16 @@
       <c r="A9" s="32">
         <v>1979</v>
       </c>
-      <c r="B9" s="175">
+      <c r="B9" s="147">
         <v>3.8737190082644628</v>
       </c>
-      <c r="C9" s="175">
+      <c r="C9" s="147">
         <v>1.8243966942148762</v>
       </c>
-      <c r="D9" s="175">
+      <c r="D9" s="147">
         <v>0</v>
       </c>
-      <c r="E9" s="175">
+      <c r="E9" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43629,16 +44842,16 @@
       <c r="A10" s="32">
         <v>1980</v>
       </c>
-      <c r="B10" s="175">
+      <c r="B10" s="147">
         <v>3.3518446601941743</v>
       </c>
-      <c r="C10" s="175">
+      <c r="C10" s="147">
         <v>1.5071067961165048</v>
       </c>
-      <c r="D10" s="175">
+      <c r="D10" s="147">
         <v>0</v>
       </c>
-      <c r="E10" s="175">
+      <c r="E10" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43646,16 +44859,16 @@
       <c r="A11" s="32">
         <v>1981</v>
       </c>
-      <c r="B11" s="175">
+      <c r="B11" s="147">
         <v>2.8343762376237618</v>
       </c>
-      <c r="C11" s="175">
+      <c r="C11" s="147">
         <v>1.40609900990099</v>
       </c>
-      <c r="D11" s="175">
+      <c r="D11" s="147">
         <v>0</v>
       </c>
-      <c r="E11" s="175">
+      <c r="E11" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43663,16 +44876,16 @@
       <c r="A12" s="32">
         <v>1982</v>
       </c>
-      <c r="B12" s="175">
+      <c r="B12" s="147">
         <v>2.5529036269430052</v>
       </c>
-      <c r="C12" s="175">
+      <c r="C12" s="147">
         <v>1.1552829015544042</v>
       </c>
-      <c r="D12" s="175">
+      <c r="D12" s="147">
         <v>0</v>
       </c>
-      <c r="E12" s="175">
+      <c r="E12" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43680,16 +44893,16 @@
       <c r="A13" s="32">
         <v>1983</v>
       </c>
-      <c r="B13" s="175">
+      <c r="B13" s="147">
         <v>2.6090602409638555</v>
       </c>
-      <c r="C13" s="175">
+      <c r="C13" s="147">
         <v>1.0241927710843375</v>
       </c>
-      <c r="D13" s="175">
+      <c r="D13" s="147">
         <v>0</v>
       </c>
-      <c r="E13" s="175">
+      <c r="E13" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43697,16 +44910,16 @@
       <c r="A14" s="32">
         <v>1984</v>
       </c>
-      <c r="B14" s="175">
+      <c r="B14" s="147">
         <v>2.2546602502406157</v>
       </c>
-      <c r="C14" s="175">
+      <c r="C14" s="147">
         <v>0.92359576515880659</v>
       </c>
-      <c r="D14" s="175">
+      <c r="D14" s="147">
         <v>0</v>
       </c>
-      <c r="E14" s="175">
+      <c r="E14" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43714,16 +44927,16 @@
       <c r="A15" s="32">
         <v>1985</v>
       </c>
-      <c r="B15" s="175">
+      <c r="B15" s="147">
         <v>2.8085353159851301</v>
       </c>
-      <c r="C15" s="175">
+      <c r="C15" s="147">
         <v>1.1035539033457251</v>
       </c>
-      <c r="D15" s="175">
+      <c r="D15" s="147">
         <v>0</v>
       </c>
-      <c r="E15" s="175">
+      <c r="E15" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43731,16 +44944,16 @@
       <c r="A16" s="32">
         <v>1986</v>
       </c>
-      <c r="B16" s="175">
+      <c r="B16" s="147">
         <v>2.720496350364964</v>
       </c>
-      <c r="C16" s="175">
+      <c r="C16" s="147">
         <v>0.974890510948905</v>
       </c>
-      <c r="D16" s="175">
+      <c r="D16" s="147">
         <v>0</v>
       </c>
-      <c r="E16" s="175">
+      <c r="E16" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43748,16 +44961,16 @@
       <c r="A17" s="32">
         <v>1987</v>
       </c>
-      <c r="B17" s="175">
+      <c r="B17" s="147">
         <v>5.199718309859156</v>
       </c>
-      <c r="C17" s="175">
+      <c r="C17" s="147">
         <v>0.81811267605633808</v>
       </c>
-      <c r="D17" s="175">
+      <c r="D17" s="147">
         <v>0</v>
       </c>
-      <c r="E17" s="175">
+      <c r="E17" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43765,16 +44978,16 @@
       <c r="A18" s="32">
         <v>1988</v>
       </c>
-      <c r="B18" s="175">
+      <c r="B18" s="147">
         <v>7.2545325443786979</v>
       </c>
-      <c r="C18" s="175">
+      <c r="C18" s="147">
         <v>2.7930887573964496</v>
       </c>
-      <c r="D18" s="175">
+      <c r="D18" s="147">
         <v>0</v>
       </c>
-      <c r="E18" s="175">
+      <c r="E18" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43782,16 +44995,16 @@
       <c r="A19" s="32">
         <v>1989</v>
       </c>
-      <c r="B19" s="175">
+      <c r="B19" s="147">
         <v>7.5372387096774203</v>
       </c>
-      <c r="C19" s="175">
+      <c r="C19" s="147">
         <v>3.1849548387096775</v>
       </c>
-      <c r="D19" s="175">
+      <c r="D19" s="147">
         <v>0</v>
       </c>
-      <c r="E19" s="175">
+      <c r="E19" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43799,16 +45012,16 @@
       <c r="A20" s="32">
         <v>1990</v>
       </c>
-      <c r="B20" s="175">
+      <c r="B20" s="147">
         <v>8.1226136189747518</v>
       </c>
-      <c r="C20" s="175">
+      <c r="C20" s="147">
         <v>3.5106472838561591</v>
       </c>
-      <c r="D20" s="175">
+      <c r="D20" s="147">
         <v>0</v>
       </c>
-      <c r="E20" s="175">
+      <c r="E20" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43816,16 +45029,16 @@
       <c r="A21" s="32">
         <v>1991</v>
       </c>
-      <c r="B21" s="175">
+      <c r="B21" s="147">
         <v>12.112281938325992</v>
       </c>
-      <c r="C21" s="175">
+      <c r="C21" s="147">
         <v>4.3250748898678424</v>
       </c>
-      <c r="D21" s="175">
+      <c r="D21" s="147">
         <v>0</v>
       </c>
-      <c r="E21" s="175">
+      <c r="E21" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43833,16 +45046,16 @@
       <c r="A22" s="32">
         <v>1992</v>
       </c>
-      <c r="B22" s="175">
+      <c r="B22" s="147">
         <v>14.310295081967212</v>
       </c>
-      <c r="C22" s="175">
+      <c r="C22" s="147">
         <v>4.4099101924447606</v>
       </c>
-      <c r="D22" s="175">
+      <c r="D22" s="147">
         <v>0</v>
       </c>
-      <c r="E22" s="175">
+      <c r="E22" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43850,16 +45063,16 @@
       <c r="A23" s="32">
         <v>1993</v>
       </c>
-      <c r="B23" s="175">
+      <c r="B23" s="147">
         <v>16.780932871972318</v>
       </c>
-      <c r="C23" s="175">
+      <c r="C23" s="147">
         <v>4.8956013840830446</v>
       </c>
-      <c r="D23" s="175">
+      <c r="D23" s="147">
         <v>0</v>
       </c>
-      <c r="E23" s="175">
+      <c r="E23" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43867,16 +45080,16 @@
       <c r="A24" s="32">
         <v>1994</v>
       </c>
-      <c r="B24" s="175">
+      <c r="B24" s="147">
         <v>22.578655870445345</v>
       </c>
-      <c r="C24" s="175">
+      <c r="C24" s="147">
         <v>6.1309797570850204</v>
       </c>
-      <c r="D24" s="175">
+      <c r="D24" s="147">
         <v>0</v>
       </c>
-      <c r="E24" s="175">
+      <c r="E24" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43884,16 +45097,16 @@
       <c r="A25" s="32">
         <v>1995</v>
       </c>
-      <c r="B25" s="175">
+      <c r="B25" s="147">
         <v>27.553322834645666</v>
       </c>
-      <c r="C25" s="175">
+      <c r="C25" s="147">
         <v>6.7821732283464549</v>
       </c>
-      <c r="D25" s="175">
+      <c r="D25" s="147">
         <v>0</v>
       </c>
-      <c r="E25" s="175">
+      <c r="E25" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43901,16 +45114,16 @@
       <c r="A26" s="32">
         <v>1996</v>
       </c>
-      <c r="B26" s="175">
+      <c r="B26" s="147">
         <v>29.754309751434029</v>
       </c>
-      <c r="C26" s="175">
+      <c r="C26" s="147">
         <v>7.2827839388145312</v>
       </c>
-      <c r="D26" s="175">
+      <c r="D26" s="147">
         <v>0</v>
       </c>
-      <c r="E26" s="175">
+      <c r="E26" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43918,16 +45131,16 @@
       <c r="A27" s="32">
         <v>1997</v>
       </c>
-      <c r="B27" s="175">
+      <c r="B27" s="147">
         <v>30.6432</v>
       </c>
-      <c r="C27" s="175">
+      <c r="C27" s="147">
         <v>7.5276560747663552</v>
       </c>
-      <c r="D27" s="175">
+      <c r="D27" s="147">
         <v>0</v>
       </c>
-      <c r="E27" s="175">
+      <c r="E27" s="147">
         <v>0</v>
       </c>
     </row>
@@ -43935,16 +45148,16 @@
       <c r="A28" s="32">
         <v>1998</v>
       </c>
-      <c r="B28" s="175">
+      <c r="B28" s="147">
         <v>33.610306748466257</v>
       </c>
-      <c r="C28" s="175">
+      <c r="C28" s="147">
         <v>6.3881226993865026</v>
       </c>
-      <c r="D28" s="175">
+      <c r="D28" s="147">
         <v>0</v>
       </c>
-      <c r="E28" s="175">
+      <c r="E28" s="147">
         <v>18.72958986993865</v>
       </c>
     </row>
@@ -43952,16 +45165,16 @@
       <c r="A29" s="32">
         <v>1999</v>
       </c>
-      <c r="B29" s="175">
+      <c r="B29" s="147">
         <v>33.403159663865544</v>
       </c>
-      <c r="C29" s="175">
+      <c r="C29" s="147">
         <v>5.1997310924369753</v>
       </c>
-      <c r="D29" s="175">
+      <c r="D29" s="147">
         <v>0.98307710924369762</v>
       </c>
-      <c r="E29" s="175">
+      <c r="E29" s="147">
         <v>23.473966386554622</v>
       </c>
     </row>
@@ -43969,16 +45182,16 @@
       <c r="A30" s="32">
         <v>2000</v>
       </c>
-      <c r="B30" s="175">
+      <c r="B30" s="147">
         <v>32.549853658536584</v>
       </c>
-      <c r="C30" s="175">
+      <c r="C30" s="147">
         <v>5.26009756097561</v>
       </c>
-      <c r="D30" s="175">
+      <c r="D30" s="147">
         <v>1.1445553170731708</v>
       </c>
-      <c r="E30" s="175">
+      <c r="E30" s="147">
         <v>23.05095687804878</v>
       </c>
     </row>
@@ -43986,16 +45199,16 @@
       <c r="A31" s="32">
         <v>2001</v>
       </c>
-      <c r="B31" s="175">
+      <c r="B31" s="147">
         <v>33.060806324110672</v>
       </c>
-      <c r="C31" s="175">
+      <c r="C31" s="147">
         <v>4.9324268774703564</v>
       </c>
-      <c r="D31" s="175">
+      <c r="D31" s="147">
         <v>5.6858678893280636</v>
       </c>
-      <c r="E31" s="175">
+      <c r="E31" s="147">
         <v>25.52981008695652</v>
       </c>
     </row>
@@ -44003,16 +45216,16 @@
       <c r="A32" s="32">
         <v>2002</v>
       </c>
-      <c r="B32" s="175">
+      <c r="B32" s="147">
         <v>37.806443579766537</v>
       </c>
-      <c r="C32" s="175">
+      <c r="C32" s="147">
         <v>5.0002178988326849</v>
       </c>
-      <c r="D32" s="175">
+      <c r="D32" s="147">
         <v>7.1896376031128399</v>
       </c>
-      <c r="E32" s="175">
+      <c r="E32" s="147">
         <v>24.116101354085597</v>
       </c>
     </row>
@@ -44020,16 +45233,16 @@
       <c r="A33" s="32">
         <v>2003</v>
       </c>
-      <c r="B33" s="175">
+      <c r="B33" s="147">
         <v>37.265321739130435</v>
       </c>
-      <c r="C33" s="175">
+      <c r="C33" s="147">
         <v>5.0893043478260873</v>
       </c>
-      <c r="D33" s="175">
+      <c r="D33" s="147">
         <v>9.9843670956521748</v>
       </c>
-      <c r="E33" s="175">
+      <c r="E33" s="147">
         <v>24.967749130434783</v>
       </c>
     </row>
@@ -44037,16 +45250,16 @@
       <c r="A34" s="32">
         <v>2004</v>
       </c>
-      <c r="B34" s="175">
+      <c r="B34" s="147">
         <v>37.673266278454207</v>
       </c>
-      <c r="C34" s="175">
+      <c r="C34" s="147">
         <v>5.0416008470089988</v>
       </c>
-      <c r="D34" s="175">
+      <c r="D34" s="147">
         <v>15.421513130757015</v>
       </c>
-      <c r="E34" s="175">
+      <c r="E34" s="147">
         <v>34.472057850714663</v>
       </c>
     </row>
@@ -44054,16 +45267,16 @@
       <c r="A35" s="32">
         <v>2005</v>
       </c>
-      <c r="B35" s="175">
+      <c r="B35" s="147">
         <v>38.673548387096773</v>
       </c>
-      <c r="C35" s="175">
+      <c r="C35" s="147">
         <v>5.1045161290322572</v>
       </c>
-      <c r="D35" s="175">
+      <c r="D35" s="147">
         <v>15.995003870967739</v>
       </c>
-      <c r="E35" s="175">
+      <c r="E35" s="147">
         <v>33.081414193548383</v>
       </c>
     </row>
@@ -44071,16 +45284,16 @@
       <c r="A36" s="32">
         <v>2006</v>
       </c>
-      <c r="B36" s="175">
+      <c r="B36" s="147">
         <v>39.072222000000004</v>
       </c>
-      <c r="C36" s="175">
+      <c r="C36" s="147">
         <v>5.315343999999997</v>
       </c>
-      <c r="D36" s="175">
+      <c r="D36" s="147">
         <v>16.248888999999998</v>
       </c>
-      <c r="E36" s="175">
+      <c r="E36" s="147">
         <v>31.741550999999998</v>
       </c>
     </row>
